--- a/data/credit_bond_all_2026-09-08.xlsx
+++ b/data/credit_bond_all_2026-09-08.xlsx
@@ -745,7 +745,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6800/1.6000</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0400/2.0100</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8450/1.8400</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>1.8200/--</t>
+          <t>1.8100/1.7700</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
@@ -2345,7 +2345,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="X10" s="3"/>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>1.81%~1.91%</t>
+        </is>
+      </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -2486,7 +2490,11 @@
           <t>09-08 18:00</t>
         </is>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>102683551.IB</t>
+        </is>
+      </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -2565,7 +2573,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X11" s="3"/>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>1.61%~1.71%</t>
+        </is>
+      </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -2706,7 +2718,11 @@
           <t>09-08 18:00</t>
         </is>
       </c>
-      <c r="C12" s="3"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>102683561.IB</t>
+        </is>
+      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -2785,7 +2801,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X12" s="3"/>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>1.74%~1.84%</t>
+        </is>
+      </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -2913,7 +2933,9 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="AZ12" s="3"/>
+      <c r="AZ12" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
@@ -2926,7 +2948,11 @@
           <t>09-08 18:00</t>
         </is>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>102683560.IB</t>
+        </is>
+      </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
           <t>3+2</t>
@@ -2965,7 +2991,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7400/--</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -3005,7 +3031,11 @@
           <t>5+</t>
         </is>
       </c>
-      <c r="X13" s="3"/>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>1.67%~1.77%</t>
+        </is>
+      </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3142,7 +3172,11 @@
           <t>09-08 18:00</t>
         </is>
       </c>
-      <c r="C14" s="3"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>102683549.IB</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -3181,7 +3215,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6800/1.6400</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -3221,7 +3255,11 @@
           <t>4+</t>
         </is>
       </c>
-      <c r="X14" s="3"/>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>1.61%~1.71%</t>
+        </is>
+      </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3362,7 +3400,11 @@
           <t>09-08 18:00</t>
         </is>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>102683552.IB</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -3401,7 +3443,7 @@
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0700/--</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
@@ -3441,7 +3483,11 @@
           <t>8+</t>
         </is>
       </c>
-      <c r="X15" s="3"/>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>2.30%~2.40%</t>
+        </is>
+      </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -3582,7 +3628,11 @@
           <t>09-08 18:00</t>
         </is>
       </c>
-      <c r="C16" s="3"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>102683553.IB</t>
+        </is>
+      </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -3621,7 +3671,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0700/--</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
@@ -3661,7 +3711,11 @@
           <t>8+</t>
         </is>
       </c>
-      <c r="X16" s="3"/>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>2.67%~2.77%</t>
+        </is>
+      </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -3798,7 +3852,11 @@
           <t>09-08 18:00</t>
         </is>
       </c>
-      <c r="C17" s="3"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>102683554.IB</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
           <t>3+2</t>
@@ -3877,7 +3935,11 @@
           <t>7+</t>
         </is>
       </c>
-      <c r="X17" s="3"/>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>2.72%~2.82%</t>
+        </is>
+      </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -4014,7 +4076,11 @@
           <t>09-08 18:00</t>
         </is>
       </c>
-      <c r="C18" s="3"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>102683550.IB</t>
+        </is>
+      </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -4053,7 +4119,7 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9200/--</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
@@ -4093,7 +4159,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X18" s="3"/>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>1.85%~1.95%</t>
+        </is>
+      </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -4217,7 +4287,9 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="AZ18" s="3"/>
+      <c r="AZ18" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
@@ -4230,7 +4302,11 @@
           <t>09-08 18:00</t>
         </is>
       </c>
-      <c r="C19" s="3"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>102683565.IB</t>
+        </is>
+      </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -4309,7 +4385,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X19" s="3"/>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>1.75%~1.85%</t>
+        </is>
+      </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -4437,7 +4517,9 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="AZ19" s="3"/>
+      <c r="AZ19" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
@@ -4450,7 +4532,11 @@
           <t>09-08 18:00</t>
         </is>
       </c>
-      <c r="C20" s="3"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>012682218.IB</t>
+        </is>
+      </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
           <t>0.37Y</t>
@@ -4489,7 +4575,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5200/1.5000</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -4529,7 +4615,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X20" s="3"/>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>1.49%~1.53%</t>
+        </is>
+      </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -4666,7 +4756,11 @@
           <t>09-08 18:00</t>
         </is>
       </c>
-      <c r="C21" s="3"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>012682217.IB</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
           <t>0.74Y</t>
@@ -4745,7 +4839,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X21" s="3"/>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>1.53%~1.57%</t>
+        </is>
+      </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -4886,7 +4984,11 @@
           <t>09-08 18:00</t>
         </is>
       </c>
-      <c r="C22" s="3"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>102683555.IB</t>
+        </is>
+      </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -4925,7 +5027,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7400/--</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -4965,7 +5067,11 @@
           <t>5+</t>
         </is>
       </c>
-      <c r="X22" s="3"/>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>1.66%~1.76%</t>
+        </is>
+      </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -5093,7 +5199,9 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="AZ22" s="3"/>
+      <c r="AZ22" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
@@ -5106,7 +5214,11 @@
           <t>09-08 18:00</t>
         </is>
       </c>
-      <c r="C23" s="3"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>102683559.IB</t>
+        </is>
+      </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
@@ -5145,7 +5257,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7100/--</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
@@ -5185,7 +5297,11 @@
           <t>5+</t>
         </is>
       </c>
-      <c r="X23" s="3"/>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>1.63%~1.73%</t>
+        </is>
+      </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -5369,7 +5485,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6500/--</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -5409,7 +5525,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X24" s="3"/>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>1.59%~1.69%</t>
+        </is>
+      </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -5589,7 +5709,7 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8700/1.8650</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
@@ -5629,7 +5749,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X25" s="3"/>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>1.82%~1.92%</t>
+        </is>
+      </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -5849,7 +5973,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="X26" s="3"/>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>1.61%~1.71%</t>
+        </is>
+      </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -6033,7 +6161,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7700/1.7000</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -6073,7 +6201,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X27" s="3"/>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>1.51%~1.61%</t>
+        </is>
+      </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -6194,7 +6326,7 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26中财10</t>
+          <t>26连城03</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6204,7 +6336,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>246023.SH</t>
+          <t>283871.SH</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -6213,41 +6345,49 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>20.0</v>
+        <v>9.0</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>26连城01</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>4.59Y</t>
+        </is>
+      </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.9832</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0000/--</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>中国中金财富证券有限公司</t>
+          <t>连云港市城建控股集团有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>B- 45.81</t>
+          <t>C+ 30.75</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6257,7 +6397,7 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>09-08 16:00</t>
+          <t>09-08 15:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -6274,10 +6414,14 @@
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X28" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>1.99%~2.09%</t>
+        </is>
+      </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -6286,17 +6430,17 @@
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>江苏省-连云港市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金拟全部用于偿还到期债券本金。[23中财C3,24中财G2,24中财C1,22中财G2]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还发行人到期或回售的公司债券本金。[23连城03]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,国金证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司,申万宏源证券有限公司,招商证券股份有限公司,东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
@@ -6307,7 +6451,7 @@
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr">
@@ -6317,12 +6461,12 @@
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>中国中金财富证券有限公司2026年面向专业投资者公开发行公司债券(第五期)(品种二)</t>
+          <t>连云港市城建控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ28" s="3" t="inlineStr">
@@ -6348,32 +6492,32 @@
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
@@ -6406,7 +6550,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26连城03</t>
+          <t>26惠控03</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6416,43 +6560,43 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>283871.SH</t>
+          <t>283945.SH</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26连城01</t>
+          <t>24惠控03</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>4.59Y</t>
+          <t>2.49Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.9832</t>
+          <t>1.7810</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -6462,12 +6606,12 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>连云港市城建控股集团有限公司</t>
+          <t>无锡市惠山国有投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.75</t>
+          <t>B- 35.14</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6487,36 +6631,40 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X29" s="3"/>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>2.15%~2.25%</t>
+        </is>
+      </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>江苏省-连云港市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还发行人到期或回售的公司债券本金。[23连城03]</t>
+          <t>本期债券募集资金扣除发行费用后,仅用于偿还回售的公司债券本金[23惠控02]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,华泰联合证券有限责任公司,申万宏源证券有限公司,招商证券股份有限公司,东吴证券股份有限公司</t>
+          <t>天风证券股份有限公司,国联民生证券承销保荐有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
@@ -6537,7 +6685,7 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>连云港市城建控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>无锡市惠山国有投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6547,7 +6695,7 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2031-09-10</t>
+          <t>2033-09-09</t>
         </is>
       </c>
       <c r="AK29" s="3"/>
@@ -6563,7 +6711,7 @@
       </c>
       <c r="AN29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AO29" s="3" t="inlineStr">
@@ -6573,22 +6721,22 @@
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
@@ -6626,7 +6774,7 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26惠控03</t>
+          <t>26惠控02</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6636,12 +6784,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>283945.SH</t>
+          <t>283944.SH</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
@@ -6650,14 +6798,14 @@
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
@@ -6717,7 +6865,11 @@
           <t>5+</t>
         </is>
       </c>
-      <c r="X30" s="3"/>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>1.97%~2.07%</t>
+        </is>
+      </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -6757,7 +6909,7 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>无锡市惠山国有投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
+          <t>无锡市惠山国有投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -6767,7 +6919,7 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2033-09-09</t>
+          <t>2031-09-09</t>
         </is>
       </c>
       <c r="AK30" s="3"/>
@@ -6846,22 +6998,22 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26惠控02</t>
+          <t>26大同D2</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>09-08 18:00</t>
+          <t>09-08 17:00</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>283944.SH</t>
+          <t>283781.SH</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.48Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
@@ -6870,29 +7022,29 @@
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.80 ~ 2.09</t>
         </is>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>24惠控03</t>
+          <t>25大同D1</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>2.49Y</t>
+          <t>52D</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.7810</t>
+          <t>2.6553</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -6902,12 +7054,12 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>无锡市惠山国有投资控股集团有限公司</t>
+          <t>大同证券有限责任公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>B- 35.14</t>
+          <t>C- 12.36</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -6917,7 +7069,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>09-08 15:00</t>
+          <t>09-08 13:00</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
@@ -6934,10 +7086,14 @@
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
-        </is>
-      </c>
-      <c r="X31" s="3"/>
+          <t>7+</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>2.49%~2.53%</t>
+        </is>
+      </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -6946,28 +7102,28 @@
       <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>山西省-大同市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,仅用于偿还回售的公司债券本金[23惠控02]</t>
+          <t>本期债券发行规模不超过人民币2.00亿元(含2.00亿元)。本期债券募集资金扣除发行费用后,1.50亿元用于偿还到期短期公司债券,剩余部分用于补充流动资金。[26大同D1]</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>天风证券股份有限公司,国联民生证券承销保荐有限公司</t>
+          <t>大同证券有限责任公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG31" s="3" t="inlineStr">
@@ -6977,7 +7133,7 @@
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>无锡市惠山国有投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
+          <t>大同证券有限责任公司2026年面向专业投资者非公开发行短期公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -6987,7 +7143,7 @@
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
+          <t>2027-03-03</t>
         </is>
       </c>
       <c r="AK31" s="3"/>
@@ -7008,32 +7164,32 @@
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
@@ -7066,22 +7222,18 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26大同D2</t>
+          <t>26合川城投PPN006</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>09-08 17:00</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>283781.SH</t>
-        </is>
-      </c>
+          <t>09-08 18:00</t>
+        </is>
+      </c>
+      <c r="C32" s="3"/>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>0.48Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
@@ -7090,29 +7242,29 @@
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.09</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>25大同D1</t>
+          <t>24渝合02</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>52D</t>
+          <t>2.98Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>2.6553</t>
+          <t>1.8650</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -7122,12 +7274,12 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>大同证券有限责任公司</t>
+          <t>重庆市合川城市建设投资(集团)有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C- 12.36</t>
+          <t>C- 16.65</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7137,7 +7289,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>09-08 13:00</t>
+          <t>09-08 09:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -7157,7 +7309,11 @@
           <t>7+</t>
         </is>
       </c>
-      <c r="X32" s="3"/>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>1.87%~1.97%</t>
+        </is>
+      </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -7166,38 +7322,38 @@
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>山西省-大同市</t>
+          <t>重庆市-合川区</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过人民币2.00亿元(含2.00亿元)。本期债券募集资金扣除发行费用后,1.50亿元用于偿还到期短期公司债券,剩余部分用于补充流动资金。[26大同D1]</t>
+          <t>发行人本次定向工具注册额度为30亿元,本期债务融资工具基础发行规模为0亿元,发行规模上限为2亿元。资金全部用于偿还公司存续的债务融资工具[23合川城投MTN004B]</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>大同证券有限责任公司</t>
+          <t>重庆银行股份有限公司,中泰证券股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>大同证券有限责任公司2026年面向专业投资者非公开发行短期公司债券(第二期)</t>
+          <t>重庆市合川城市建设投资(集团)有限公司2026年度第六期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7207,13 +7363,17 @@
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2027-03-03</t>
-        </is>
-      </c>
-      <c r="AK32" s="3"/>
+          <t>2029-09-09</t>
+        </is>
+      </c>
+      <c r="AK32" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL32" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AM32" s="3" t="inlineStr">
@@ -7228,7 +7388,7 @@
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP32" s="3" t="inlineStr">
@@ -7238,22 +7398,22 @@
       </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7286,7 +7446,7 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26合川城投PPN006</t>
+          <t>26商丘发展PPN002</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7301,49 +7461,49 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.0</v>
+        <v>9.0</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>24渝合02</t>
+          <t>26商丘发展PPN001</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>2.98Y</t>
+          <t>2.94Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.8650</t>
+          <t>1.8676</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9200/1.8000</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>重庆市合川城市建设投资(集团)有限公司</t>
+          <t>商丘市发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>C- 16.65</t>
+          <t>B- 39.77</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7370,10 +7530,14 @@
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
-        </is>
-      </c>
-      <c r="X33" s="3"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>1.87%~1.97%</t>
+        </is>
+      </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -7382,17 +7546,17 @@
       <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>重庆市-合川区</t>
+          <t>河南省-商丘市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>发行人本次定向工具注册额度为30亿元,本期债务融资工具基础发行规模为0亿元,发行规模上限为2亿元。资金全部用于偿还公司存续的债务融资工具[23合川城投MTN004B]</t>
+          <t>本期定向债务融资工具发行金额为9亿元,拟全部用于偿还到期债务融资工具本金[24商丘发展PPN002,24商丘发展PPN003]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>重庆银行股份有限公司,中泰证券股份有限公司,华夏银行股份有限公司</t>
+          <t>中信银行股份有限公司,中信建投证券股份有限公司,东方证券股份有限公司,中泰证券股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
@@ -7413,7 +7577,7 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>重庆市合川城市建设投资(集团)有限公司2026年度第六期定向债务融资工具</t>
+          <t>商丘市发展投资集团有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7458,22 +7622,22 @@
       </c>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
@@ -7501,12 +7665,14 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="AZ33" s="3"/>
+      <c r="AZ33" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26商丘发展PPN002</t>
+          <t>26东北Y2</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -7514,56 +7680,60 @@
           <t>09-08 18:00</t>
         </is>
       </c>
-      <c r="C34" s="3"/>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>524939.SZ</t>
+        </is>
+      </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.90 ~ 2.90</t>
         </is>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>26商丘发展PPN001</t>
+          <t>26东北Y1</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>2.94Y</t>
+          <t>4.87Y+N</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.8676</t>
+          <t>2.2505</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.2500/2.2000</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>商丘市发展投资集团有限公司</t>
+          <t>东北证券股份有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>B- 39.77</t>
+          <t>C 28.52</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7573,7 +7743,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>09-08 09:00</t>
+          <t>09-08 15:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -7583,42 +7753,50 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X34" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>2.13%~2.23%</t>
+        </is>
+      </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z34" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>河南省-商丘市</t>
+          <t>吉林省-长春市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行金额为9亿元,拟全部用于偿还到期债务融资工具本金[24商丘发展PPN002,24商丘发展PPN003]</t>
+          <t>本期债券发行总额为不超过10亿元(含10亿元)，募集资金扣除发行费用后，拟全部用于偿还债券期限在1年期以上的公司债券。[23东北01,24东北C1]</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中信建投证券股份有限公司,东方证券股份有限公司,中泰证券股份有限公司</t>
+          <t>长城证券股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>证券公司次级债</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
@@ -7628,72 +7806,68 @@
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>商丘市发展投资集团有限公司2026年度第二期定向债务融资工具</t>
+          <t>东北证券股份有限公司2026年面向专业投资者公开发行永续次级债券(第二期)</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
-        </is>
-      </c>
-      <c r="AK34" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-10</t>
+        </is>
+      </c>
+      <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AM34" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -7708,12 +7882,12 @@
       </c>
       <c r="AW34" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX34" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY34" s="3" t="inlineStr">
@@ -7726,49 +7900,45 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26中信建投CP016</t>
+          <t>26新开发银行债02A(BC)</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>09-08 17:00</t>
+          <t>09-08 18:00</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>072610177.IB</t>
+          <t>292680033.IB</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>0.52Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>30.0</v>
+        <v>55.0</v>
       </c>
       <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>1.39 ~ 1.69</t>
+        </is>
+      </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>26中信建投CP015</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t>171D</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K35" s="3"/>
+      <c r="L35" s="3"/>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.4828</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
@@ -7778,12 +7948,12 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>新开发银行</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>B- 43.38</t>
+          <t>C+ 32.08</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -7803,7 +7973,7 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="U35" s="3"/>
@@ -7813,11 +7983,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X35" s="3" t="inlineStr">
-        <is>
-          <t>1.45%~1.49%</t>
-        </is>
-      </c>
+      <c r="X35" s="3"/>
       <c r="Y35" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -7826,24 +7992,28 @@
       <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
-        </is>
-      </c>
-      <c r="AB35" s="3"/>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>本期债券发行的募集资金净额将用作发行人的公司一般用途，且将用于为可持续发展项目或进程提供融资、为利益相关方提供获益的产品、服务或成果及／或致力于加速实现本行成员国的可持续发展目标。本期债券项下不超过100％的募集资金净额可汇至境外使用，用于提供人民币融资及／或兑换成其他货币。</t>
+        </is>
+      </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>中国银行股份有限公司,中国农业银行股份有限公司,中国建设银行股份有限公司,中国工商银行股份有限公司,渤海银行股份有限公司,汇丰银行(中国)有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>证券公司短期融资券</t>
+          <t>国际机构债券</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>外商独资企业</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr">
@@ -7853,7 +8023,7 @@
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司2026年度第十六期短期融资券</t>
+          <t>新开发银行2026年度第二期人民币债券(债券通)(品种一)</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -7863,23 +8033,23 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2027-03-19</t>
+          <t>2029-09-14</t>
         </is>
       </c>
       <c r="AK35" s="3"/>
       <c r="AL35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="AM35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AO35" s="3" t="inlineStr">
@@ -7887,29 +8057,25 @@
           <t>金融</t>
         </is>
       </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="AP35" s="3"/>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>其他银行</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -7937,12 +8103,14 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="AZ35" s="3"/>
+      <c r="AZ35" s="4" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26东北Y2</t>
+          <t>26新开发银行债02B(BC)</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -7952,43 +8120,35 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>524939.SZ</t>
+          <t>292680034.IB</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>1.49 ~ 1.79</t>
         </is>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>2.26</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>26东北Y1</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t>4.87Y+N</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>2.2505</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
@@ -7998,12 +8158,12 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>东北证券股份有限公司</t>
+          <t>新开发银行</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C 28.52</t>
+          <t>C+ 32.08</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8013,7 +8173,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>09-08 15:00</t>
+          <t>09-08 09:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -8023,65 +8183,57 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X36" s="3" t="inlineStr">
-        <is>
-          <t>2.13%~2.23%</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X36" s="3"/>
       <c r="Y36" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z36" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>吉林省-长春市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行总额为不超过10亿元(含10亿元)，募集资金扣除发行费用后，拟全部用于偿还债券期限在1年期以上的公司债券。[23东北01,24东北C1]</t>
+          <t>本期债券发行的募集资金净额将用作发行人的公司一般用途，且将用于为可持续发展项目或进程提供融资、为利益相关方提供获益的产品、服务或成果及／或致力于加速实现本行成员国的可持续发展目标。本期债券项下不超过100％的募集资金净额可汇至境外使用，用于提供人民币融资及／或兑换成其他货币。</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>长城证券股份有限公司</t>
+          <t>中国银行股份有限公司,中国农业银行股份有限公司,中国建设银行股份有限公司,中国工商银行股份有限公司,渤海银行股份有限公司,汇丰银行(中国)有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>证券公司次级债</t>
+          <t>国际机构债券</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>外商独资企业</t>
         </is>
       </c>
       <c r="AG36" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>东北证券股份有限公司2026年面向专业投资者公开发行永续次级债券(第二期)</t>
+          <t>新开发银行2026年度第二期人民币债券(债券通)(品种二)</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -8091,60 +8243,60 @@
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2031-09-10</t>
-        </is>
-      </c>
-      <c r="AK36" s="3"/>
+          <t>2031-09-14</t>
+        </is>
+      </c>
+      <c r="AK36" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL36" s="3" t="inlineStr">
         <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP36" s="3"/>
+      <c r="AQ36" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>商业银行</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>其他银行</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>银行</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM36" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AO36" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ36" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR36" s="3" t="inlineStr">
-        <is>
-          <t>证券</t>
-        </is>
-      </c>
-      <c r="AS36" s="3" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="AT36" s="3" t="inlineStr">
-        <is>
-          <t>证券</t>
-        </is>
-      </c>
-      <c r="AU36" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV36" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -8152,12 +8304,12 @@
       </c>
       <c r="AW36" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX36" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY36" s="3" t="inlineStr">
@@ -8165,12 +8317,14 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="AZ36" s="3"/>
+      <c r="AZ36" s="4" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26新开发银行债02A(BC)</t>
+          <t>26临港经济MTN003</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8180,86 +8334,102 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>292680033.IB</t>
+          <t>102683562.IB</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>7+3</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>55.0</v>
+        <v>15.0</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.39 ~ 1.69</t>
+          <t>1.60 ~ 2.20</t>
         </is>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>25临港经济MTN001</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>8.88Y</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>2.0913</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>上海临港经济发展(集团)有限公司</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>B- 43.35</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>09-08 09:00</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3"/>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>新开发银行</t>
-        </is>
-      </c>
-      <c r="P37" s="3" t="inlineStr">
-        <is>
-          <t>C+ 32.08</t>
-        </is>
-      </c>
-      <c r="Q37" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="R37" s="3" t="inlineStr">
-        <is>
-          <t>09-08 09:00</t>
-        </is>
-      </c>
-      <c r="S37" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X37" s="3"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>1.94%~2.04%</t>
+        </is>
+      </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z37" s="3"/>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>上海市</t>
@@ -8267,23 +8437,23 @@
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行的募集资金净额将用作发行人的公司一般用途，且将用于为可持续发展项目或进程提供融资、为利益相关方提供获益的产品、服务或成果及／或致力于加速实现本行成员国的可持续发展目标。本期债券项下不超过100％的募集资金净额可汇至境外使用，用于提供人民币融资及／或兑换成其他货币。</t>
+          <t>发行人本期中期票据拟发行金额为15亿元，用于归还发行人金融机构借款</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中国农业银行股份有限公司,中国建设银行股份有限公司,中国工商银行股份有限公司,渤海银行股份有限公司,汇丰银行(中国)有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
+          <t>上海银行股份有限公司,浙商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
       <c r="AE37" s="3" t="inlineStr">
         <is>
-          <t>国际机构债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF37" s="3" t="inlineStr">
         <is>
-          <t>外商独资企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG37" s="3" t="inlineStr">
@@ -8293,7 +8463,7 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>新开发银行2026年度第二期人民币债券(债券通)(品种一)</t>
+          <t>上海临港经济发展(集团)有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8303,54 +8473,58 @@
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2029-09-14</t>
+          <t>2036-09-09</t>
         </is>
       </c>
       <c r="AK37" s="3"/>
       <c r="AL37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AM37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AN37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP37" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>其他银行</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2033-09-09</t>
         </is>
       </c>
       <c r="AV37" s="3" t="inlineStr">
@@ -8360,7 +8534,7 @@
       </c>
       <c r="AW37" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX37" s="3" t="inlineStr">
@@ -8373,12 +8547,14 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="AZ37" s="3"/>
+      <c r="AZ37" s="4" t="n">
+        <v>0.005</v>
+      </c>
     </row>
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26新开发银行债02B(BC)</t>
+          <t>26蓉城轨交MTN003</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8388,7 +8564,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>292680034.IB</t>
+          <t>102683564.IB</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -8397,61 +8573,69 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.49 ~ 1.79</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>26蓉轨03</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>4.60Y</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>1.7356</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>1.7500/--</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>成都轨道交通集团有限公司</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>C- 24.56</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>09-08 09:00</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>新开发银行</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="inlineStr">
-        <is>
-          <t>C+ 32.08</t>
-        </is>
-      </c>
-      <c r="Q38" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t>09-08 09:00</t>
-        </is>
-      </c>
-      <c r="S38" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U38" s="3"/>
@@ -8461,7 +8645,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X38" s="3"/>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>1.68%~1.78%</t>
+        </is>
+      </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -8470,28 +8658,28 @@
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行的募集资金净额将用作发行人的公司一般用途，且将用于为可持续发展项目或进程提供融资、为利益相关方提供获益的产品、服务或成果及／或致力于加速实现本行成员国的可持续发展目标。本期债券项下不超过100％的募集资金净额可汇至境外使用，用于提供人民币融资及／或兑换成其他货币。</t>
+          <t>发行人本期债务融资工具拟募集资金10亿元，拟全部用于偿付有息债务本息</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中国农业银行股份有限公司,中国建设银行股份有限公司,中国工商银行股份有限公司,渤海银行股份有限公司,汇丰银行(中国)有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
+          <t>中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>国际机构债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
         <is>
-          <t>外商独资企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG38" s="3" t="inlineStr">
@@ -8501,7 +8689,7 @@
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>新开发银行2026年度第二期人民币债券(债券通)(品种二)</t>
+          <t>成都轨道交通集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
@@ -8511,53 +8699,53 @@
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2031-09-14</t>
-        </is>
-      </c>
-      <c r="AK38" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-09</t>
+        </is>
+      </c>
+      <c r="AK38" s="3"/>
       <c r="AL38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AM38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AN38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP38" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>其他银行</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>铁路运输</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -8590,7 +8778,7 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26临港经济MTN003</t>
+          <t>26泰交通MTN002</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -8598,56 +8786,60 @@
           <t>09-08 18:00</t>
         </is>
       </c>
-      <c r="C39" s="3"/>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>102683557.IB</t>
+        </is>
+      </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>7+3</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>15.0</v>
+        <v>2.3</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>25临港经济MTN001</t>
+          <t>26泰交通MTN001</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>8.88Y</t>
+          <t>2.38Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>2.0913</t>
+          <t>1.6805</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7600/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>上海临港经济发展(集团)有限公司</t>
+          <t>泰州市交通产业集团有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>B- 43.35</t>
+          <t>C- 17.75</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -8657,7 +8849,7 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>09-08 09:00</t>
+          <t>09-08 14:00</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -8674,33 +8866,33 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="X39" s="3"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>1.62%~1.72%</t>
+        </is>
+      </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z39" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据拟发行金额为15亿元，用于归还发行人金融机构借款</t>
+          <t>发行人本期中期票据拟发行2.3亿元,全部用于偿还债务融资工具本金[26泰交通SCP003]</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>上海银行股份有限公司,浙商银行股份有限公司</t>
+          <t>国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
@@ -8721,7 +8913,7 @@
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>上海临港经济发展(集团)有限公司2026年度第三期中期票据</t>
+          <t>泰州市交通产业集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -8731,10 +8923,14 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2036-09-09</t>
-        </is>
-      </c>
-      <c r="AK39" s="3"/>
+          <t>2029-09-09</t>
+        </is>
+      </c>
+      <c r="AK39" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL39" s="3" t="inlineStr">
         <is>
           <t>2026-09-10</t>
@@ -8757,7 +8953,7 @@
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
@@ -8767,22 +8963,22 @@
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>综合交运基础设施</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>综合交运基础设施</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
         <is>
-          <t>2033-09-09</t>
+          <t/>
         </is>
       </c>
       <c r="AV39" s="3" t="inlineStr">
@@ -8792,7 +8988,7 @@
       </c>
       <c r="AW39" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX39" s="3" t="inlineStr">
@@ -8805,12 +9001,14 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="AZ39" s="3"/>
+      <c r="AZ39" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26蓉城轨交MTN003</t>
+          <t>26平安租赁CP005</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -8818,56 +9016,60 @@
           <t>09-08 18:00</t>
         </is>
       </c>
-      <c r="C40" s="3"/>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>042680308.IB</t>
+        </is>
+      </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.97Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.40 ~ 1.52</t>
         </is>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>26蓉轨03</t>
+          <t>26平安租赁CP004</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>4.60Y</t>
+          <t>359D</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.7356</t>
+          <t>1.5702</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5650/1.5200</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>成都轨道交通集团有限公司</t>
+          <t>平安国际融资租赁有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C- 24.56</t>
+          <t>C- 20.16</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -8894,10 +9096,14 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X40" s="3"/>
+          <t>4-</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>1.57%~1.61%</t>
+        </is>
+      </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -8906,12 +9112,12 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>发行人本期债务融资工具拟募集资金10亿元，拟全部用于偿付有息债务本息</t>
+          <t>发行人本次发行短期融资券拟募集资金5亿元，拟全部用于偿还发行人到期债务融资工具[25平安租赁CP009]</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
@@ -8922,12 +9128,12 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>短期融资券(CP)</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG40" s="3" t="inlineStr">
@@ -8937,7 +9143,7 @@
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>成都轨道交通集团有限公司2026年度第三期中期票据</t>
+          <t>平安国际融资租赁有限公司2026年度第五期短期融资券</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
@@ -8947,10 +9153,14 @@
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
-        </is>
-      </c>
-      <c r="AK40" s="3"/>
+          <t>2027-08-28</t>
+        </is>
+      </c>
+      <c r="AK40" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL40" s="3" t="inlineStr">
         <is>
           <t>2026-09-10</t>
@@ -8968,32 +9178,32 @@
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>铁路运输</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
@@ -9021,12 +9231,14 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="AZ40" s="3"/>
+      <c r="AZ40" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26泰交通MTN002</t>
+          <t>26隧道股份SCP006</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -9034,56 +9246,60 @@
           <t>09-08 18:00</t>
         </is>
       </c>
-      <c r="C41" s="3"/>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>012682216.IB</t>
+        </is>
+      </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.35Y</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>2.3</v>
+        <v>10.0</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.30 ~ 1.50</t>
         </is>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>26泰交通MTN001</t>
+          <t>26隧道股份SCP005</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>2.38Y</t>
+          <t>73D</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>1.6805</t>
+          <t>1.4600</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5000/1.4800</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>泰州市交通产业集团有限公司</t>
+          <t>上海隧道工程股份有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>C- 17.75</t>
+          <t>C- 23.87</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9093,7 +9309,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>09-08 14:00</t>
+          <t>09-08 10:00</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
@@ -9110,35 +9326,39 @@
       <c r="V41" s="3"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X41" s="3"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>1.47%~1.51%</t>
+        </is>
+      </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据拟发行2.3亿元,全部用于偿还债务融资工具本金[26泰交通SCP003]</t>
+          <t>本期超短期融资券发行规模为10亿元,募集资金拟用于偿还发行人债务融资工具。[23隧道K2]</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司</t>
+          <t>兴业银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
       <c r="AE41" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF41" s="3" t="inlineStr">
@@ -9153,7 +9373,7 @@
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>泰州市交通产业集团有限公司2026年度第二期中期票据</t>
+          <t>上海隧道工程股份有限公司2026年度第六期超短期融资券</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
@@ -9163,12 +9383,12 @@
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
+          <t>2027-01-16</t>
         </is>
       </c>
       <c r="AK41" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL41" s="3" t="inlineStr">
@@ -9188,32 +9408,32 @@
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP41" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ41" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>综合交运基础设施</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
         <is>
-          <t>综合交运基础设施</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AT41" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU41" s="3" t="inlineStr">
@@ -9241,12 +9461,14 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="AZ41" s="3"/>
+      <c r="AZ41" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26平安租赁CP005</t>
+          <t>26夏商SCP023</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -9254,10 +9476,14 @@
           <t>09-08 18:00</t>
         </is>
       </c>
-      <c r="C42" s="3"/>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>012682219.IB</t>
+        </is>
+      </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>0.97Y</t>
+          <t>0.16Y</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
@@ -9266,44 +9492,44 @@
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.52</t>
+          <t>1.30 ~ 1.49</t>
         </is>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>26平安租赁CP004</t>
+          <t>26夏商SCP022</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>359D</t>
+          <t>52D</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1.5702</t>
+          <t>1.4898</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5300/1.4800</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>平安国际融资租赁有限公司</t>
+          <t>厦门夏商集团有限公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>C- 20.16</t>
+          <t>C- 20.00</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9330,40 +9556,44 @@
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
-        </is>
-      </c>
-      <c r="X42" s="3"/>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>1.47%~1.51%</t>
+        </is>
+      </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行短期融资券拟募集资金5亿元，拟全部用于偿还发行人到期债务融资工具[25平安租赁CP009]</t>
+          <t>发行人本期发行超短期融资券5亿元，扣除承销费后，拟全部用于偿还发行人本部银行借款。</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司</t>
+          <t>交通银行股份有限公司</t>
         </is>
       </c>
       <c r="AD42" s="3"/>
       <c r="AE42" s="3" t="inlineStr">
         <is>
-          <t>短期融资券(CP)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF42" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG42" s="3" t="inlineStr">
@@ -9373,7 +9603,7 @@
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>平安国际融资租赁有限公司2026年度第五期短期融资券</t>
+          <t>厦门夏商集团有限公司2026年度第二十三期超短期融资券</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
@@ -9383,14 +9613,10 @@
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2027-08-28</t>
-        </is>
-      </c>
-      <c r="AK42" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="AK42" s="3"/>
       <c r="AL42" s="3" t="inlineStr">
         <is>
           <t>2026-09-10</t>
@@ -9408,7 +9634,7 @@
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP42" s="3" t="inlineStr">
@@ -9418,22 +9644,22 @@
       </c>
       <c r="AQ42" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT42" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU42" s="3" t="inlineStr">
@@ -9461,12 +9687,14 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="AZ42" s="3"/>
+      <c r="AZ42" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26隧道股份SCP006</t>
+          <t>26苏科技城MTN005</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -9474,41 +9702,45 @@
           <t>09-08 18:00</t>
         </is>
       </c>
-      <c r="C43" s="3"/>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>102690027.IB</t>
+        </is>
+      </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>0.35Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>26隧道股份SCP005</t>
+          <t>26苏科技城MTN004</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>73D</t>
+          <t>2.95Y+N</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>1.4600</t>
+          <t>1.8244</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -9518,12 +9750,12 @@
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>上海隧道工程股份有限公司</t>
+          <t>苏州科技城发展集团有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C- 23.87</t>
+          <t>D+ 8.15</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -9533,7 +9765,7 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>09-08 10:00</t>
+          <t>09-08 14:00</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
@@ -9550,35 +9782,39 @@
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="X43" s="3"/>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>1.78%~1.88%</t>
+        </is>
+      </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z43" s="3"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行规模为10亿元,募集资金拟用于偿还发行人债务融资工具。[23隧道K2]</t>
+          <t>本期中期票据发行规模2亿元,募集资金拟全部用于偿还发行人到期的债务融资工具。[23苏科技城MTN007]</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>中信证券股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD43" s="3"/>
       <c r="AE43" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF43" s="3" t="inlineStr">
@@ -9593,7 +9829,7 @@
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>上海隧道工程股份有限公司2026年度第六期超短期融资券</t>
+          <t>苏州科技城发展集团有限公司2026年度第五期中期票据</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
@@ -9603,12 +9839,12 @@
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2027-01-16</t>
+          <t>2029-09-09</t>
         </is>
       </c>
       <c r="AK43" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL43" s="3" t="inlineStr">
@@ -9628,27 +9864,27 @@
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP43" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ43" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
@@ -9668,7 +9904,7 @@
       </c>
       <c r="AW43" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX43" s="3" t="inlineStr">
@@ -9686,7 +9922,7 @@
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP023</t>
+          <t>26华能SCP011</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -9694,56 +9930,60 @@
           <t>09-08 18:00</t>
         </is>
       </c>
-      <c r="C44" s="3"/>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>012682220.IB</t>
+        </is>
+      </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>0.16Y</t>
+          <t>0.18Y</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>5.0</v>
+        <v>25.0</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.49</t>
+          <t>1.26 ~ 1.46</t>
         </is>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP022</t>
+          <t>26华能SCP010</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>52D</t>
+          <t>43D</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1.4898</t>
+          <t>1.4600</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.4700/--</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司</t>
+          <t>华能国际电力股份有限公司</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>C- 20.00</t>
+          <t>B- 44.68</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -9770,29 +10010,33 @@
       <c r="V44" s="3"/>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
-        </is>
-      </c>
-      <c r="X44" s="3"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>1.44%~1.48%</t>
+        </is>
+      </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z44" s="3"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>河北省-保定市</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行超短期融资券5亿元，扣除承销费后，拟全部用于偿还发行人本部银行借款。</t>
+          <t>发行人本期发行超短期融资券发行规模为人民币25亿元,募集资金将用于补充发行人营运资金、调整债务结构、偿还银行借款及即将到期的债券。</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>交通银行股份有限公司</t>
+          <t>渤海银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD44" s="3"/>
@@ -9803,7 +10047,7 @@
       </c>
       <c r="AF44" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG44" s="3" t="inlineStr">
@@ -9813,7 +10057,7 @@
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司2026年度第二十三期超短期融资券</t>
+          <t>华能国际电力股份有限公司2026年度第十一期超短期融资券</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
@@ -9823,7 +10067,7 @@
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="AK44" s="3"/>
@@ -9849,27 +10093,27 @@
       </c>
       <c r="AP44" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ44" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>火电</t>
         </is>
       </c>
       <c r="AT44" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU44" s="3" t="inlineStr">
@@ -9897,12 +10141,14 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="AZ44" s="3"/>
+      <c r="AZ44" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26苏科技城MTN005</t>
+          <t>26晋江城投MTN001B</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -9910,56 +10156,60 @@
           <t>09-08 18:00</t>
         </is>
       </c>
-      <c r="C45" s="3"/>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>102683556.IB</t>
+        </is>
+      </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>2.0</v>
+        <v>4.5</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.60 ~ 2.40</t>
         </is>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>26苏科技城MTN004</t>
+          <t>25晋江城投MTN006</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>2.95Y+N</t>
+          <t>4.18Y</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1.8244</t>
+          <t>1.7910</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8200/1.7700</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>苏州科技城发展集团有限公司</t>
+          <t>福建省晋江城市建设投资开发集团有限责任公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.15</t>
+          <t>C- 24.32</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -9969,7 +10219,7 @@
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>09-08 14:00</t>
+          <t>09-08 09:00</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
@@ -9986,29 +10236,33 @@
       <c r="V45" s="3"/>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X45" s="3"/>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>1.77%~1.87%</t>
+        </is>
+      </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z45" s="3"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>福建省-泉州市</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模2亿元,募集资金拟全部用于偿还发行人到期的债务融资工具。[23苏科技城MTN007]</t>
+          <t>本期中期票据发行8.70亿元,拟用于偿还债务融资工具本金。[25晋江城投SCP003B]</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,宁波银行股份有限公司</t>
+          <t>中信银行股份有限公司,国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD45" s="3"/>
@@ -10029,7 +10283,7 @@
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>苏州科技城发展集团有限公司2026年度第五期中期票据</t>
+          <t>福建省晋江城市建设投资开发集团有限责任公司2026年度第一期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
@@ -10039,14 +10293,10 @@
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
-        </is>
-      </c>
-      <c r="AK45" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-09</t>
+        </is>
+      </c>
+      <c r="AK45" s="3"/>
       <c r="AL45" s="3" t="inlineStr">
         <is>
           <t>2026-09-10</t>
@@ -10064,12 +10314,12 @@
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP45" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ45" s="3" t="inlineStr">
@@ -10079,17 +10329,17 @@
       </c>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT45" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU45" s="3" t="inlineStr">
@@ -10104,7 +10354,7 @@
       </c>
       <c r="AW45" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX45" s="3" t="inlineStr">
@@ -10117,12 +10367,14 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="AZ45" s="3"/>
+      <c r="AZ45" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26华能SCP011</t>
+          <t>26腾旺产投02</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -10130,56 +10382,60 @@
           <t>09-08 18:00</t>
         </is>
       </c>
-      <c r="C46" s="3"/>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>520447.SZ</t>
+        </is>
+      </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>0.18Y</t>
+          <t>5+2</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>25.0</v>
+        <v>2.0</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.26 ~ 1.46</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>26华能SCP010</t>
+          <t>26腾旺产投01</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>43D</t>
+          <t>4.74Y+2.00Y</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1.4600</t>
+          <t>2.0172</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0300/1.9800</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>华能国际电力股份有限公司</t>
+          <t>肇庆腾旺产业投资集团有限公司</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>B- 44.68</t>
+          <t>B 55.00</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -10189,7 +10445,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>09-08 09:00</t>
+          <t>09-08 15:00</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
@@ -10199,85 +10455,101 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X46" s="3"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>2.05%~2.15%</t>
+        </is>
+      </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z46" s="3"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
-          <t>河北省-保定市</t>
+          <t>广东省-肇庆市</t>
         </is>
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行超短期融资券发行规模为人民币25亿元,募集资金将用于补充发行人营运资金、调整债务结构、偿还银行借款及即将到期的债券。</t>
+          <t>本期公司债券募集资金扣除发行费用后，拟将不超过2.00亿元用于偿还到期债务</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司,中国民生银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD46" s="3"/>
+          <t>天风证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr">
+        <is>
+          <t>广东粤财融资担保集团有限公司</t>
+        </is>
+      </c>
       <c r="AE46" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF46" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG46" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>华能国际电力股份有限公司2026年度第十一期超短期融资券</t>
+          <t>肇庆腾旺产业投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ46" s="3" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="AK46" s="3"/>
+          <t>2033-09-10</t>
+        </is>
+      </c>
+      <c r="AK46" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL46" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AM46" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
           <t>产业</t>
@@ -10285,42 +10557,42 @@
       </c>
       <c r="AP46" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ46" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>房地产</t>
         </is>
       </c>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>房地产服务</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
         <is>
-          <t>火电</t>
+          <t>其他房地产服务</t>
         </is>
       </c>
       <c r="AT46" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU46" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-10</t>
         </is>
       </c>
       <c r="AV46" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW46" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX46" s="3" t="inlineStr">
@@ -10338,7 +10610,7 @@
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26晋江城投MTN001B</t>
+          <t>26中电金投MTN002(并购)</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -10346,41 +10618,45 @@
           <t>09-08 18:00</t>
         </is>
       </c>
-      <c r="C47" s="3"/>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>102683563.IB</t>
+        </is>
+      </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.40</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>25晋江城投MTN006</t>
+          <t>26金投K1</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>4.18Y</t>
+          <t>2.72Y</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>1.7910</t>
+          <t>1.6920</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
@@ -10390,12 +10666,12 @@
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>福建省晋江城市建设投资开发集团有限责任公司</t>
+          <t>中电金投控股有限公司</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>C- 24.32</t>
+          <t>C+ 32.53</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -10422,29 +10698,33 @@
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
-        </is>
-      </c>
-      <c r="X47" s="3"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>1.67%~1.77%</t>
+        </is>
+      </c>
       <c r="Y47" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z47" s="3"/>
       <c r="AA47" s="3" t="inlineStr">
         <is>
-          <t>福建省-泉州市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB47" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行8.70亿元,拟用于偿还债务融资工具本金。[25晋江城投SCP003B]</t>
+          <t>本期中期票据基础发行规模为0亿元,发行规模上限为6.50亿元,其中3.0678亿元拟用于偿还到期有息债务,3.36742亿元拟用于置换发行人过去一年内通过大宗交易参股并购武汉达梦数据库股份有限公司(688692.SH)股份所投入的自有资金,置换后的资金及本期债券剩余募集资金拟用于发行人及其子公司偿还有息债务等。[24中电K1]</t>
         </is>
       </c>
       <c r="AC47" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,国信证券股份有限公司</t>
+          <t>招商证券股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD47" s="3"/>
@@ -10455,7 +10735,7 @@
       </c>
       <c r="AF47" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG47" s="3" t="inlineStr">
@@ -10465,7 +10745,7 @@
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>福建省晋江城市建设投资开发集团有限责任公司2026年度第一期中期票据(品种二)</t>
+          <t>中电金投控股有限公司2026年度第二期中期票据(并购)</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
@@ -10475,10 +10755,14 @@
       </c>
       <c r="AJ47" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
-        </is>
-      </c>
-      <c r="AK47" s="3"/>
+          <t>2029-09-09</t>
+        </is>
+      </c>
+      <c r="AK47" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL47" s="3" t="inlineStr">
         <is>
           <t>2026-09-10</t>
@@ -10496,32 +10780,28 @@
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP47" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP47" s="3"/>
       <c r="AQ47" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT47" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU47" s="3" t="inlineStr">
@@ -10554,7 +10834,7 @@
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>26腾旺产投02</t>
+          <t>国新发04</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -10564,43 +10844,43 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>520447.SZ</t>
+          <t>246053.SH</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>5+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>2.0</v>
+        <v>30.0</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.20 ~ 2.10</t>
         </is>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>26腾旺产投01</t>
+          <t>25国新发展MTN001(科创债)</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>4.74Y+2.00Y</t>
+          <t>2.14Y</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>2.0172</t>
+          <t>1.6469</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
@@ -10610,12 +10890,12 @@
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>肇庆腾旺产业投资集团有限公司</t>
+          <t>国新发展投资管理有限公司</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>B 55.00</t>
+          <t>C+ 32.22</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -10625,7 +10905,7 @@
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>09-08 15:00</t>
+          <t>09-08 16:00</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr">
@@ -10642,40 +10922,36 @@
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X48" s="3"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>1.61%~1.71%</t>
+        </is>
+      </c>
       <c r="Y48" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z48" s="3" t="inlineStr">
-        <is>
           <t>AAA</t>
         </is>
       </c>
+      <c r="Z48" s="3"/>
       <c r="AA48" s="3" t="inlineStr">
         <is>
-          <t>广东省-肇庆市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB48" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后，拟将不超过2.00亿元用于偿还到期债务</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将30亿元全部用于偿还有息负债。</t>
         </is>
       </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
-          <t>天风证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD48" s="3" t="inlineStr">
-        <is>
-          <t>广东粤财融资担保集团有限公司</t>
-        </is>
-      </c>
+          <t>中信证券股份有限公司,国新证券股份有限公司,招商证券股份有限公司,国泰海通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD48" s="3"/>
       <c r="AE48" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -10683,34 +10959,30 @@
       </c>
       <c r="AF48" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG48" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH48" s="3" t="inlineStr">
         <is>
-          <t>肇庆腾旺产业投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>国新发展投资管理有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI48" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ48" s="3" t="inlineStr">
         <is>
-          <t>2033-09-10</t>
-        </is>
-      </c>
-      <c r="AK48" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2029-09-10</t>
+        </is>
+      </c>
+      <c r="AK48" s="3"/>
       <c r="AL48" s="3" t="inlineStr">
         <is>
           <t/>
@@ -10728,47 +11000,43 @@
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP48" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP48" s="3"/>
       <c r="AQ48" s="3" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>房地产服务</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">
         <is>
-          <t>其他房地产服务</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT48" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU48" s="3" t="inlineStr">
         <is>
-          <t>2031-09-10</t>
+          <t/>
         </is>
       </c>
       <c r="AV48" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW48" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX48" s="3" t="inlineStr">
@@ -10786,7 +11054,7 @@
     <row r="49" customHeight="true" ht="18.0">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>26中电金投MTN002(并购)</t>
+          <t>26中财G9</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -10794,56 +11062,60 @@
           <t>09-08 18:00</t>
         </is>
       </c>
-      <c r="C49" s="3"/>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>246022.SH</t>
+        </is>
+      </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>6.5</v>
+        <v>20.0</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>26金投K1</t>
+          <t>26中财G7</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>2.72Y</t>
+          <t>2.79Y</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>1.6920</t>
+          <t>1.6667</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6700/1.6500</t>
         </is>
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>中电金投控股有限公司</t>
+          <t>中国中金财富证券有限公司</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.53</t>
+          <t>B- 45.81</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
@@ -10853,7 +11125,7 @@
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>09-08 09:00</t>
+          <t>09-08 16:00</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr">
@@ -10863,17 +11135,21 @@
       </c>
       <c r="T49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="U49" s="3"/>
       <c r="V49" s="3"/>
       <c r="W49" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X49" s="3"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>1.60%~1.70%</t>
+        </is>
+      </c>
       <c r="Y49" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -10882,23 +11158,23 @@
       <c r="Z49" s="3"/>
       <c r="AA49" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB49" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模为0亿元,发行规模上限为6.50亿元,其中3.0678亿元拟用于偿还到期有息债务,3.36742亿元拟用于置换发行人过去一年内通过大宗交易参股并购武汉达梦数据库股份有限公司(688692.SH)股份所投入的自有资金,置换后的资金及本期债券剩余募集资金拟用于发行人及其子公司偿还有息债务等。[24中电K1]</t>
+          <t>本期债券的募集资金拟全部用于偿还到期债券本金。[23中财C3,24中财G2,24中财C1,22中财G2]</t>
         </is>
       </c>
       <c r="AC49" s="3" t="inlineStr">
         <is>
-          <t>招商证券股份有限公司,中国建设银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司,国金证券股份有限公司</t>
         </is>
       </c>
       <c r="AD49" s="3"/>
       <c r="AE49" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF49" s="3" t="inlineStr">
@@ -10908,12 +11184,12 @@
       </c>
       <c r="AG49" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH49" s="3" t="inlineStr">
         <is>
-          <t>中电金投控股有限公司2026年度第二期中期票据(并购)</t>
+          <t>中国中金财富证券有限公司2026年面向专业投资者公开发行公司债券(第五期)(品种一)</t>
         </is>
       </c>
       <c r="AI49" s="3" t="inlineStr">
@@ -10923,35 +11199,35 @@
       </c>
       <c r="AJ49" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
-        </is>
-      </c>
-      <c r="AK49" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-10</t>
+        </is>
+      </c>
+      <c r="AK49" s="3"/>
       <c r="AL49" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AM49" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
           <t>金融</t>
         </is>
       </c>
-      <c r="AP49" s="3"/>
+      <c r="AP49" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
       <c r="AQ49" s="3" t="inlineStr">
         <is>
           <t>非银</t>
@@ -10959,17 +11235,17 @@
       </c>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT49" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU49" s="3" t="inlineStr">
@@ -11002,7 +11278,7 @@
     <row r="50" customHeight="true" ht="18.0">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>国新发04</t>
+          <t>26金轨02</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -11012,58 +11288,58 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>246053.SH</t>
+          <t>283776.SH</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>30.0</v>
+        <v>6.5</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.10</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>25国新发展MTN001(科创债)</t>
+          <t>26金轨01</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>2.14Y</t>
+          <t>2.75Y</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>1.6469</t>
+          <t>1.7527</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7600/1.6972</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>国新发展投资管理有限公司</t>
+          <t>金华市轨道交通集团有限公司</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.22</t>
+          <t>C- 18.45</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -11073,7 +11349,7 @@
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>09-08 16:00</t>
+          <t>09-08 15:00</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr">
@@ -11090,29 +11366,33 @@
       <c r="V50" s="3"/>
       <c r="W50" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X50" s="3"/>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>1.92%~2.02%</t>
+        </is>
+      </c>
       <c r="Y50" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z50" s="3"/>
       <c r="AA50" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>浙江省-金华市</t>
         </is>
       </c>
       <c r="AB50" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将30亿元全部用于偿还有息负债。</t>
+          <t>本期债券发行规模不超过6.5亿元(含6.5亿元),拟将募集资金扣除发行费用后5亿元用于偿还到期的公司债券本金,1.5亿元用于偿还有息负债,不用于临时补流</t>
         </is>
       </c>
       <c r="AC50" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国新证券股份有限公司,招商证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD50" s="3"/>
@@ -11123,7 +11403,7 @@
       </c>
       <c r="AF50" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG50" s="3" t="inlineStr">
@@ -11133,17 +11413,17 @@
       </c>
       <c r="AH50" s="3" t="inlineStr">
         <is>
-          <t>国新发展投资管理有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>金华市轨道交通集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI50" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ50" s="3" t="inlineStr">
         <is>
-          <t>2029-09-10</t>
+          <t>2031-09-10</t>
         </is>
       </c>
       <c r="AK50" s="3"/>
@@ -11164,28 +11444,32 @@
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP50" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="AQ50" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT50" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU50" s="3" t="inlineStr">
@@ -11218,17 +11502,17 @@
     <row r="51" customHeight="true" ht="18.0">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>26中财G9</t>
+          <t>26产基K2</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>09-08 18:00</t>
+          <t>09-08 17:00</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>246022.SH</t>
+          <t>283887.SH</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -11237,49 +11521,49 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>20.0</v>
+        <v>5.0</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>26中财G7</t>
+          <t>26产基K1</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>2.79Y</t>
+          <t>2.52Y</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>1.6667</t>
+          <t>1.6999</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7400/1.6500</t>
         </is>
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>中国中金财富证券有限公司</t>
+          <t>湖南省财信产业基金管理有限公司</t>
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
-          <t>B- 45.81</t>
+          <t>A- 69.65</t>
         </is>
       </c>
       <c r="Q51" s="3" t="inlineStr">
@@ -11289,7 +11573,7 @@
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>09-08 16:00</t>
+          <t>09-08 15:00</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
@@ -11306,40 +11590,48 @@
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X51" s="3"/>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>1.77%~1.87%</t>
+        </is>
+      </c>
       <c r="Y51" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z51" s="3"/>
       <c r="AA51" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB51" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金拟全部用于偿还到期债券本金。[23中财C3,24中财G2,24中财C1,22中财G2]</t>
+          <t>本期债券发行总额不超过5亿元(含5亿元)，扣除发行费用后，4亿元用于投向科技创新领域的基金出资，包括置换前期出资和新增出资，剩余资金用于补流。</t>
         </is>
       </c>
       <c r="AC51" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,国金证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD51" s="3"/>
+          <t>财信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr">
+        <is>
+          <t>湖南财信金融控股集团有限公司</t>
+        </is>
+      </c>
       <c r="AE51" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF51" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG51" s="3" t="inlineStr">
@@ -11349,12 +11641,12 @@
       </c>
       <c r="AH51" s="3" t="inlineStr">
         <is>
-          <t>中国中金财富证券有限公司2026年面向专业投资者公开发行公司债券(第五期)(品种一)</t>
+          <t>湖南省财信产业基金管理有限公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI51" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ51" s="3" t="inlineStr">
@@ -11383,11 +11675,7 @@
           <t>金融</t>
         </is>
       </c>
-      <c r="AP51" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
+      <c r="AP51" s="3"/>
       <c r="AQ51" s="3" t="inlineStr">
         <is>
           <t>非银</t>
@@ -11395,17 +11683,17 @@
       </c>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT51" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU51" s="3" t="inlineStr">
@@ -11415,7 +11703,7 @@
       </c>
       <c r="AV51" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW51" s="3" t="inlineStr">
@@ -11438,7 +11726,7 @@
     <row r="52" customHeight="true" ht="18.0">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>26金轨02</t>
+          <t>26绿投02</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -11448,7 +11736,7 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>283776.SH</t>
+          <t>283844.SH</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -11457,49 +11745,49 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>6.5</v>
+        <v>2.7</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>26金轨01</t>
+          <t>26绿投01</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>2.75Y</t>
+          <t>2.42Y</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>1.7527</t>
+          <t>1.7250</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
         <is>
-          <t>1.7600/--</t>
+          <t>--/1.6700</t>
         </is>
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>金华市轨道交通集团有限公司</t>
+          <t>扬州绿色产业投资发展控股(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>C- 18.45</t>
+          <t>C- 11.91</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
@@ -11509,7 +11797,7 @@
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>09-08 15:00</t>
+          <t>09-08 16:00</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr">
@@ -11526,32 +11814,40 @@
       <c r="V52" s="3"/>
       <c r="W52" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X52" s="3"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>1.99%~2.09%</t>
+        </is>
+      </c>
       <c r="Y52" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z52" s="3"/>
       <c r="AA52" s="3" t="inlineStr">
         <is>
-          <t>浙江省-金华市</t>
+          <t>江苏省-扬州市</t>
         </is>
       </c>
       <c r="AB52" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过6.5亿元(含6.5亿元),拟将募集资金扣除发行费用后5亿元用于偿还到期的公司债券本金,1.5亿元用于偿还有息负债,不用于临时补流</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[23绿投02]</t>
         </is>
       </c>
       <c r="AC52" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD52" s="3"/>
+          <t>华泰联合证券有限责任公司,中信证券股份有限公司,申万宏源证券有限公司</t>
+        </is>
+      </c>
+      <c r="AD52" s="3" t="inlineStr">
+        <is>
+          <t>扬州经济技术开发区开发(集团)有限公司</t>
+        </is>
+      </c>
       <c r="AE52" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -11569,7 +11865,7 @@
       </c>
       <c r="AH52" s="3" t="inlineStr">
         <is>
-          <t>金华市轨道交通集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>扬州绿色产业投资发展控股(集团)有限责任公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI52" s="3" t="inlineStr">
@@ -11605,7 +11901,7 @@
       </c>
       <c r="AP52" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ52" s="3" t="inlineStr">
@@ -11615,17 +11911,17 @@
       </c>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT52" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU52" s="3" t="inlineStr">
@@ -11635,7 +11931,7 @@
       </c>
       <c r="AV52" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW52" s="3" t="inlineStr">
@@ -11658,22 +11954,18 @@
     <row r="53" customHeight="true" ht="18.0">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>26产基K2</t>
+          <t>26宁海国资PPN001</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>09-08 17:00</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>283887.SH</t>
-        </is>
-      </c>
+          <t>09-08 18:00</t>
+        </is>
+      </c>
+      <c r="C53" s="3"/>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
@@ -11682,44 +11974,44 @@
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>26产基K1</t>
+          <t>21宁海国投债01(柜台)</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>2.52Y</t>
+          <t>2.30Y</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>1.6999</t>
+          <t>1.6688</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
-          <t>1.6900/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>湖南省财信产业基金管理有限公司</t>
+          <t>宁海县国有资产投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>A- 69.65</t>
+          <t>D- 1.35</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
@@ -11729,7 +12021,7 @@
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>09-08 15:00</t>
+          <t>09-08 09:00</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr">
@@ -11739,7 +12031,7 @@
       </c>
       <c r="T53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U53" s="3"/>
@@ -11749,7 +12041,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X53" s="3"/>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>1.87%~1.97%</t>
+        </is>
+      </c>
       <c r="Y53" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -11758,27 +12054,23 @@
       <c r="Z53" s="3"/>
       <c r="AA53" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>浙江省-宁波市</t>
         </is>
       </c>
       <c r="AB53" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行总额不超过5亿元(含5亿元)，扣除发行费用后，4亿元用于投向科技创新领域的基金出资，包括置换前期出资和新增出资，剩余资金用于补流。</t>
+          <t>本次定向债务融资工具发行金额5亿元,募集资金拟全部用于偿还到期的债务融资工具本金[21宁海国资PPN001]</t>
         </is>
       </c>
       <c r="AC53" s="3" t="inlineStr">
         <is>
-          <t>财信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD53" s="3" t="inlineStr">
-        <is>
-          <t>湖南财信金融控股集团有限公司</t>
-        </is>
-      </c>
+          <t>宁波银行股份有限公司,东吴证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD53" s="3"/>
       <c r="AE53" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF53" s="3" t="inlineStr">
@@ -11788,12 +12080,12 @@
       </c>
       <c r="AG53" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH53" s="3" t="inlineStr">
         <is>
-          <t>湖南省财信产业基金管理有限公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)</t>
+          <t>宁海县国有资产投资控股集团有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI53" s="3" t="inlineStr">
@@ -11803,13 +12095,13 @@
       </c>
       <c r="AJ53" s="3" t="inlineStr">
         <is>
-          <t>2029-09-10</t>
+          <t>2031-09-09</t>
         </is>
       </c>
       <c r="AK53" s="3"/>
       <c r="AL53" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AM53" s="3" t="inlineStr">
@@ -11819,48 +12111,52 @@
       </c>
       <c r="AN53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP53" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP53" s="3" t="inlineStr">
+        <is>
+          <t>7*无效</t>
+        </is>
+      </c>
       <c r="AQ53" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT53" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU53" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-09</t>
         </is>
       </c>
       <c r="AV53" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW53" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX53" s="3" t="inlineStr">
@@ -11878,7 +12174,7 @@
     <row r="54" customHeight="true" ht="18.0">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>26绿投02</t>
+          <t>26越产03</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -11888,7 +12184,7 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>283844.SH</t>
+          <t>524994.SZ</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -11897,49 +12193,49 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>2.7</v>
+        <v>5.0</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>26绿投01</t>
+          <t>26越秀产投MTN001(科创债)</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>2.42Y</t>
+          <t>4.91Y</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>1.7250</t>
+          <t>1.9112</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9500/1.9100</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>扬州绿色产业投资发展控股(集团)有限责任公司</t>
+          <t>广州越秀产业投资有限公司</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>C- 11.91</t>
+          <t>C- 22.22</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
@@ -11966,34 +12262,34 @@
       <c r="V54" s="3"/>
       <c r="W54" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X54" s="3"/>
       <c r="Y54" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z54" s="3"/>
       <c r="AA54" s="3" t="inlineStr">
         <is>
-          <t>江苏省-扬州市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB54" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[23绿投02]</t>
+          <t>本期公司债券的募集资金扣除发行费用后拟用于偿付到期公司债券本金[23越产03]</t>
         </is>
       </c>
       <c r="AC54" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,中信证券股份有限公司,申万宏源证券有限公司</t>
+          <t>中信证券股份有限公司,华泰联合证券有限责任公司,广发证券股份有限公司</t>
         </is>
       </c>
       <c r="AD54" s="3" t="inlineStr">
         <is>
-          <t>扬州经济技术开发区开发(集团)有限公司</t>
+          <t>广州越秀集团股份有限公司,广州越秀资本控股集团股份有限公司</t>
         </is>
       </c>
       <c r="AE54" s="3" t="inlineStr">
@@ -12008,17 +12304,17 @@
       </c>
       <c r="AG54" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH54" s="3" t="inlineStr">
         <is>
-          <t>扬州绿色产业投资发展控股(集团)有限责任公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>广州越秀产业投资有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI54" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ54" s="3" t="inlineStr">
@@ -12044,32 +12340,28 @@
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP54" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP54" s="3"/>
       <c r="AQ54" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT54" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU54" s="3" t="inlineStr">
@@ -12102,7 +12394,7 @@
     <row r="55" customHeight="true" ht="18.0">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>26宁海国资PPN001</t>
+          <t>26博融02</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -12110,56 +12402,60 @@
           <t>09-08 18:00</t>
         </is>
       </c>
-      <c r="C55" s="3"/>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>283817.SH</t>
+        </is>
+      </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>5.0</v>
+        <v>8.67</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.90 ~ 2.80</t>
         </is>
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>21宁海国投债01(柜台)</t>
+          <t>26博融01</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>2.30Y</t>
+          <t>4.88Y</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>1.6688</t>
+          <t>2.1671</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.2000/2.1500</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>宁海县国有资产投资控股集团有限公司</t>
+          <t>江苏博融农业发展有限公司</t>
         </is>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
-          <t>D- 1.35</t>
+          <t>C 30.00</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
@@ -12169,7 +12465,7 @@
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>09-08 09:00</t>
+          <t>09-08 15:00</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr">
@@ -12179,42 +12475,50 @@
       </c>
       <c r="T55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X55" s="3"/>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>2.17%~2.27%</t>
+        </is>
+      </c>
       <c r="Y55" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3" t="inlineStr">
         <is>
-          <t>浙江省-宁波市</t>
+          <t>江苏省-徐州市</t>
         </is>
       </c>
       <c r="AB55" s="3" t="inlineStr">
         <is>
-          <t>本次定向债务融资工具发行金额5亿元,募集资金拟全部用于偿还到期的债务融资工具本金[21宁海国资PPN001]</t>
+          <t>本期公司债券发行金额不超过8.67亿元(含8.67亿元)，募集资金扣除发行费用后，全部用于偿还到期公司债券本金[23 博融02]</t>
         </is>
       </c>
       <c r="AC55" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司,东吴证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD55" s="3"/>
+          <t>国泰海通证券股份有限公司,天风证券股份有限公司,东吴证券股份有限公司,国联民生证券承销保荐有限公司,湘财证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD55" s="3" t="inlineStr">
+        <is>
+          <t>江苏润鑫城市投资集团有限公司</t>
+        </is>
+      </c>
       <c r="AE55" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF55" s="3" t="inlineStr">
@@ -12224,12 +12528,12 @@
       </c>
       <c r="AG55" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH55" s="3" t="inlineStr">
         <is>
-          <t>宁海县国有资产投资控股集团有限公司2026年度第一期定向债务融资工具</t>
+          <t>江苏博融农业发展有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI55" s="3" t="inlineStr">
@@ -12239,48 +12543,48 @@
       </c>
       <c r="AJ55" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
+          <t>2031-09-10</t>
         </is>
       </c>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AM55" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AN55" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP55" s="3" t="inlineStr">
         <is>
-          <t>7*无效</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ55" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT55" s="3" t="inlineStr">
@@ -12290,17 +12594,17 @@
       </c>
       <c r="AU55" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
+          <t/>
         </is>
       </c>
       <c r="AV55" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW55" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX55" s="3" t="inlineStr">
@@ -12318,7 +12622,7 @@
     <row r="56" customHeight="true" ht="18.0">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>26越产03</t>
+          <t>26晋桥K1</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -12328,7 +12632,7 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>524994.SZ</t>
+          <t>524980.SZ</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -12337,34 +12641,34 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>26越秀产投MTN001(科创债)</t>
+          <t>26晋路桥MTN002</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>4.91Y</t>
+          <t>2.64Y</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>1.9112</t>
+          <t>1.8727</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
@@ -12374,12 +12678,12 @@
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>广州越秀产业投资有限公司</t>
+          <t>山西路桥建设集团有限公司</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
-          <t>C- 22.22</t>
+          <t>C 27.70</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
@@ -12389,7 +12693,7 @@
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>09-08 16:00</t>
+          <t>09-08 15:00</t>
         </is>
       </c>
       <c r="S56" s="3" t="inlineStr">
@@ -12406,36 +12710,36 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X56" s="3"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>2.10%~2.20%</t>
+        </is>
+      </c>
       <c r="Y56" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>山西省</t>
         </is>
       </c>
       <c r="AB56" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券的募集资金扣除发行费用后拟用于偿付到期公司债券本金[23越产03]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还有息负债</t>
         </is>
       </c>
       <c r="AC56" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,华泰联合证券有限责任公司,广发证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD56" s="3" t="inlineStr">
-        <is>
-          <t>广州越秀集团股份有限公司,广州越秀资本控股集团股份有限公司</t>
-        </is>
-      </c>
+          <t>五矿证券有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD56" s="3"/>
       <c r="AE56" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -12453,7 +12757,7 @@
       </c>
       <c r="AH56" s="3" t="inlineStr">
         <is>
-          <t>广州越秀产业投资有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
+          <t>山西路桥建设集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI56" s="3" t="inlineStr">
@@ -12484,28 +12788,32 @@
       </c>
       <c r="AO56" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP56" s="3"/>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP56" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="AQ56" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR56" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS56" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>市政路桥</t>
         </is>
       </c>
       <c r="AT56" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU56" s="3" t="inlineStr">
@@ -12515,7 +12823,7 @@
       </c>
       <c r="AV56" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW56" s="3" t="inlineStr">
@@ -12538,53 +12846,53 @@
     <row r="57" customHeight="true" ht="18.0">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>26博融02</t>
+          <t>26华发03</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>09-08 18:00</t>
+          <t>09-08 17:00</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>283817.SH</t>
+          <t>283215.SH</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>1+1+1</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>8.67</v>
+        <v>20.0</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.80</t>
+          <t>2.60 ~ 3.15</t>
         </is>
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>26博融01</t>
+          <t>25华发06</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>4.88Y</t>
+          <t>1.12Y+3.00Y</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>2.1671</t>
+          <t>3.3228</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
@@ -12594,12 +12902,12 @@
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>江苏博融农业发展有限公司</t>
+          <t>珠海华发实业股份有限公司</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>C+ 31.31</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -12619,41 +12927,45 @@
       </c>
       <c r="T57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U57" s="3"/>
       <c r="V57" s="3"/>
       <c r="W57" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
-        </is>
-      </c>
-      <c r="X57" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>2.60%~2.70%</t>
+        </is>
+      </c>
       <c r="Y57" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z57" s="3"/>
       <c r="AA57" s="3" t="inlineStr">
         <is>
-          <t>江苏省-徐州市</t>
+          <t>广东省-珠海市</t>
         </is>
       </c>
       <c r="AB57" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券发行金额不超过8.67亿元(含8.67亿元)，募集资金扣除发行费用后，全部用于偿还到期公司债券本金[23 博融02]</t>
+          <t>本期公司债券发行规模为不超过20.00亿元(含20.00亿元),募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金以及置换到期的公司债券本金。[23华发04,21华发03]</t>
         </is>
       </c>
       <c r="AC57" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,天风证券股份有限公司,东吴证券股份有限公司,国联民生证券承销保荐有限公司,湘财证券股份有限公司</t>
+          <t>华金证券股份有限公司,西部证券股份有限公司,国泰海通证券股份有限公司,第一创业证券承销保荐有限责任公司,国联民生证券承销保荐有限公司,华福证券股份有限公司</t>
         </is>
       </c>
       <c r="AD57" s="3" t="inlineStr">
         <is>
-          <t>江苏润鑫城市投资集团有限公司</t>
+          <t>珠海华发集团有限公司</t>
         </is>
       </c>
       <c r="AE57" s="3" t="inlineStr">
@@ -12673,7 +12985,7 @@
       </c>
       <c r="AH57" s="3" t="inlineStr">
         <is>
-          <t>江苏博融农业发展有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>珠海华发实业股份有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI57" s="3" t="inlineStr">
@@ -12683,10 +12995,14 @@
       </c>
       <c r="AJ57" s="3" t="inlineStr">
         <is>
-          <t>2031-09-10</t>
-        </is>
-      </c>
-      <c r="AK57" s="3"/>
+          <t>2029-09-09</t>
+        </is>
+      </c>
+      <c r="AK57" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL57" s="3" t="inlineStr">
         <is>
           <t/>
@@ -12699,42 +13015,42 @@
       </c>
       <c r="AN57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AO57" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP57" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ57" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>房地产</t>
         </is>
       </c>
       <c r="AR57" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AS57" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>住宅楼房</t>
         </is>
       </c>
       <c r="AT57" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU57" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2027-09-09</t>
         </is>
       </c>
       <c r="AV57" s="3" t="inlineStr">
@@ -12744,7 +13060,7 @@
       </c>
       <c r="AW57" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX57" s="3" t="inlineStr">
@@ -12762,7 +13078,7 @@
     <row r="58" customHeight="true" ht="18.0">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>26晋桥K1</t>
+          <t>26济基K3</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -12772,7 +13088,7 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>524980.SZ</t>
+          <t>520470.SZ</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -12781,34 +13097,34 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>26晋路桥MTN002</t>
+          <t>26济基K2</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>2.64Y</t>
+          <t>4.41Y</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>1.8727</t>
+          <t>2.0378</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
@@ -12818,12 +13134,12 @@
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>山西路桥建设集团有限公司</t>
+          <t>济南市财政投资基金控股集团有限公司</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>C 27.70</t>
+          <t>D 4.69</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -12850,29 +13166,33 @@
       <c r="V58" s="3"/>
       <c r="W58" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X58" s="3"/>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>1.96%~2.06%</t>
+        </is>
+      </c>
       <c r="Y58" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z58" s="3"/>
       <c r="AA58" s="3" t="inlineStr">
         <is>
-          <t>山西省</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB58" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还有息负债</t>
+          <t>本期债券发行规模为不超过人民币6亿元(含6亿元)，募集资金扣除发行费用后，不超过6亿元用于基金出资或置换前期用于基金出资的自有资金</t>
         </is>
       </c>
       <c r="AC58" s="3" t="inlineStr">
         <is>
-          <t>五矿证券有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD58" s="3"/>
@@ -12893,12 +13213,12 @@
       </c>
       <c r="AH58" s="3" t="inlineStr">
         <is>
-          <t>山西路桥建设集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
+          <t>济南市财政投资基金控股集团有限公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI58" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ58" s="3" t="inlineStr">
@@ -12924,32 +13244,28 @@
       </c>
       <c r="AO58" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP58" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP58" s="3"/>
       <c r="AQ58" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR58" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS58" s="3" t="inlineStr">
         <is>
-          <t>市政路桥</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT58" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU58" s="3" t="inlineStr">
@@ -12982,68 +13298,68 @@
     <row r="59" customHeight="true" ht="18.0">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>26华发03</t>
+          <t>26城建K2</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>09-08 17:00</t>
+          <t>09-08 18:00</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>283215.SH</t>
+          <t>245938.SH</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>1+1+1</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>20.0</v>
+        <v>9.0</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2.60 ~ 3.15</t>
+          <t>1.25 ~ 2.25</t>
         </is>
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>25华发06</t>
+          <t>24京城建MTN004</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>1.12Y+3.00Y</t>
+          <t>3.19Y</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>3.3228</t>
+          <t>1.7013</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6800</t>
         </is>
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>珠海华发实业股份有限公司</t>
+          <t>北京城建集团有限责任公司</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.31</t>
+          <t>C- 23.50</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -13053,7 +13369,7 @@
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>09-08 15:00</t>
+          <t>09-08 16:00</t>
         </is>
       </c>
       <c r="S59" s="3" t="inlineStr">
@@ -13063,14 +13379,14 @@
       </c>
       <c r="T59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="U59" s="3"/>
       <c r="V59" s="3"/>
       <c r="W59" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X59" s="3"/>
@@ -13082,24 +13398,20 @@
       <c r="Z59" s="3"/>
       <c r="AA59" s="3" t="inlineStr">
         <is>
-          <t>广东省-珠海市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB59" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券发行规模为不超过20.00亿元(含20.00亿元),募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金以及置换到期的公司债券本金。[23华发04,21华发03]</t>
+          <t>本期债券发行金额为不超过18亿元(含18亿元)，募集资金拟用于生产性支出,包括偿还公司债务、补充公司流动资金等符合法律法规要求的用途。</t>
         </is>
       </c>
       <c r="AC59" s="3" t="inlineStr">
         <is>
-          <t>华金证券股份有限公司,西部证券股份有限公司,国泰海通证券股份有限公司,第一创业证券承销保荐有限责任公司,国联民生证券承销保荐有限公司,华福证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD59" s="3" t="inlineStr">
-        <is>
-          <t>珠海华发集团有限公司</t>
-        </is>
-      </c>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,招商证券股份有限公司,国信证券股份有限公司,首创证券股份有限公司,第一创业证券承销保荐有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD59" s="3"/>
       <c r="AE59" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -13117,24 +13429,20 @@
       </c>
       <c r="AH59" s="3" t="inlineStr">
         <is>
-          <t>珠海华发实业股份有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>北京城建集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI59" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ59" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
-        </is>
-      </c>
-      <c r="AK59" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-10</t>
+        </is>
+      </c>
+      <c r="AK59" s="3"/>
       <c r="AL59" s="3" t="inlineStr">
         <is>
           <t/>
@@ -13147,7 +13455,7 @@
       </c>
       <c r="AN59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AO59" s="3" t="inlineStr">
@@ -13157,42 +13465,42 @@
       </c>
       <c r="AP59" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ59" s="3" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>房屋建筑</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">
         <is>
-          <t>住宅楼房</t>
+          <t>其他房建</t>
         </is>
       </c>
       <c r="AT59" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU59" s="3" t="inlineStr">
         <is>
-          <t>2027-09-09</t>
+          <t/>
         </is>
       </c>
       <c r="AV59" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW59" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX59" s="3" t="inlineStr">
@@ -13210,7 +13518,7 @@
     <row r="60" customHeight="true" ht="18.0">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>26济基K3</t>
+          <t>26城建K1</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -13220,58 +13528,58 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>520470.SZ</t>
+          <t>245937.SH</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.10 ~ 2.10</t>
         </is>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>26济基K2</t>
+          <t>24京城建MTN004</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>4.41Y</t>
+          <t>3.19Y</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>2.0378</t>
+          <t>1.7013</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6800</t>
         </is>
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>济南市财政投资基金控股集团有限公司</t>
+          <t>北京城建集团有限责任公司</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
-          <t>D 4.69</t>
+          <t>C- 23.50</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -13281,7 +13589,7 @@
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>09-08 15:00</t>
+          <t>09-08 16:00</t>
         </is>
       </c>
       <c r="S60" s="3" t="inlineStr">
@@ -13298,29 +13606,29 @@
       <c r="V60" s="3"/>
       <c r="W60" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X60" s="3"/>
       <c r="Y60" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z60" s="3"/>
       <c r="AA60" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB60" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过人民币6亿元(含6亿元)，募集资金扣除发行费用后，不超过6亿元用于基金出资或置换前期用于基金出资的自有资金</t>
+          <t>本期债券发行金额为不超过18亿元(含18亿元)，募集资金拟用于生产性支出,包括偿还公司债务、补充公司流动资金等符合法律法规要求的用途。</t>
         </is>
       </c>
       <c r="AC60" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中国国际金融股份有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司,中国国际金融(国际)有限公司,招商证券股份有限公司,国信证券股份有限公司,首创证券股份有限公司,第一创业证券承销保荐有限责任公司</t>
         </is>
       </c>
       <c r="AD60" s="3"/>
@@ -13336,22 +13644,22 @@
       </c>
       <c r="AG60" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH60" s="3" t="inlineStr">
         <is>
-          <t>济南市财政投资基金控股集团有限公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)</t>
+          <t>北京城建集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI60" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ60" s="3" t="inlineStr">
         <is>
-          <t>2031-09-10</t>
+          <t>2029-09-10</t>
         </is>
       </c>
       <c r="AK60" s="3"/>
@@ -13372,28 +13680,32 @@
       </c>
       <c r="AO60" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP60" s="3"/>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP60" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="AQ60" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR60" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>房屋建筑</t>
         </is>
       </c>
       <c r="AS60" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>其他房建</t>
         </is>
       </c>
       <c r="AT60" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU60" s="3" t="inlineStr">
@@ -13426,68 +13738,66 @@
     <row r="61" customHeight="true" ht="18.0">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>26城建K2</t>
+          <t>26中信建投CP016</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>09-08 18:00</t>
+          <t>09-08 17:00</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>245938.SH</t>
+          <t>072610177.IB</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.52Y</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>9.0</v>
+        <v>30.0</v>
       </c>
       <c r="F61" s="3"/>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>1.25 ~ 2.25</t>
-        </is>
-      </c>
-      <c r="H61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="I61" s="3"/>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>24京城建MTN004</t>
+          <t>26中信建投CP015</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>3.19Y</t>
+          <t>171D</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>1.7013</t>
+          <t>1.4828</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5000/1.4800</t>
         </is>
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>北京城建集团有限责任公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
-          <t>C- 23.50</t>
+          <t>B- 43.38</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
@@ -13497,7 +13807,7 @@
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>09-08 16:00</t>
+          <t>09-08 09:00</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr">
@@ -13507,17 +13817,21 @@
       </c>
       <c r="T61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U61" s="3"/>
       <c r="V61" s="3"/>
       <c r="W61" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X61" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X61" s="3" t="inlineStr">
+        <is>
+          <t>1.45%~1.49%</t>
+        </is>
+      </c>
       <c r="Y61" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -13529,35 +13843,31 @@
           <t>北京市</t>
         </is>
       </c>
-      <c r="AB61" s="3" t="inlineStr">
-        <is>
-          <t>本期债券发行金额为不超过18亿元(含18亿元)，募集资金拟用于生产性支出,包括偿还公司债务、补充公司流动资金等符合法律法规要求的用途。</t>
-        </is>
-      </c>
+      <c r="AB61" s="3"/>
       <c r="AC61" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,招商证券股份有限公司,国信证券股份有限公司,首创证券股份有限公司,第一创业证券承销保荐有限责任公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD61" s="3"/>
       <c r="AE61" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司短期融资券</t>
         </is>
       </c>
       <c r="AF61" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG61" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH61" s="3" t="inlineStr">
         <is>
-          <t>北京城建集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第一期)(品种二)</t>
+          <t>中信建投证券股份有限公司2026年度第十六期短期融资券</t>
         </is>
       </c>
       <c r="AI61" s="3" t="inlineStr">
@@ -13567,53 +13877,53 @@
       </c>
       <c r="AJ61" s="3" t="inlineStr">
         <is>
-          <t>2031-09-10</t>
+          <t>2027-03-19</t>
         </is>
       </c>
       <c r="AK61" s="3"/>
       <c r="AL61" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AM61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AN61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AO61" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP61" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ61" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR61" s="3" t="inlineStr">
         <is>
-          <t>房屋建筑</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS61" s="3" t="inlineStr">
         <is>
-          <t>其他房建</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT61" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU61" s="3" t="inlineStr">
@@ -13646,7 +13956,7 @@
     <row r="62" customHeight="true" ht="18.0">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>26城建K1</t>
+          <t>26中财10</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -13656,43 +13966,35 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>245937.SH</t>
+          <t>246023.SH</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>9.0</v>
+        <v>20.0</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="K62" s="3" t="inlineStr">
-        <is>
-          <t>24京城建MTN004</t>
-        </is>
-      </c>
-      <c r="L62" s="3" t="inlineStr">
-        <is>
-          <t>3.19Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K62" s="3"/>
+      <c r="L62" s="3"/>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>1.7013</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
@@ -13702,12 +14004,12 @@
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>北京城建集团有限责任公司</t>
+          <t>中国中金财富证券有限公司</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>C- 23.50</t>
+          <t>B- 45.81</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -13734,10 +14036,14 @@
       <c r="V62" s="3"/>
       <c r="W62" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X62" s="3"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X62" s="3" t="inlineStr">
+        <is>
+          <t>1.76%~1.86%</t>
+        </is>
+      </c>
       <c r="Y62" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -13746,28 +14052,28 @@
       <c r="Z62" s="3"/>
       <c r="AA62" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB62" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行金额为不超过18亿元(含18亿元)，募集资金拟用于生产性支出,包括偿还公司债务、补充公司流动资金等符合法律法规要求的用途。</t>
+          <t>本期债券的募集资金拟全部用于偿还到期债券本金。[23中财C3,24中财G2,24中财C1,22中财G2]</t>
         </is>
       </c>
       <c r="AC62" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司,中国国际金融(国际)有限公司,招商证券股份有限公司,国信证券股份有限公司,首创证券股份有限公司,第一创业证券承销保荐有限责任公司</t>
+          <t>华泰联合证券有限责任公司,国金证券股份有限公司</t>
         </is>
       </c>
       <c r="AD62" s="3"/>
       <c r="AE62" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF62" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG62" s="3" t="inlineStr">
@@ -13777,7 +14083,7 @@
       </c>
       <c r="AH62" s="3" t="inlineStr">
         <is>
-          <t>北京城建集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第一期)(品种一)</t>
+          <t>中国中金财富证券有限公司2026年面向专业投资者公开发行公司债券(第五期)(品种二)</t>
         </is>
       </c>
       <c r="AI62" s="3" t="inlineStr">
@@ -13787,7 +14093,7 @@
       </c>
       <c r="AJ62" s="3" t="inlineStr">
         <is>
-          <t>2029-09-10</t>
+          <t>2031-09-10</t>
         </is>
       </c>
       <c r="AK62" s="3"/>
@@ -13808,32 +14114,32 @@
       </c>
       <c r="AO62" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP62" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ62" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR62" s="3" t="inlineStr">
         <is>
-          <t>房屋建筑</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS62" s="3" t="inlineStr">
         <is>
-          <t>其他房建</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT62" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU62" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-09-08.xlsx
+++ b/data/credit_bond_all_2026-09-08.xlsx
@@ -1376,74 +1376,68 @@
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>26惠控03</t>
+          <t>26冀中峰峰MTN002B(取消发行)</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>09-08 19:00</t>
+          <t>09-08 18:00</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>283945.SH</t>
+          <t>DY102683553.IB</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>4.0</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F6" s="3"/>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>69.44</v>
-      </c>
+          <t>2.20 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>24惠控03</t>
+          <t>25冀中峰峰MTN005</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>2.49Y</t>
+          <t>1.29Y</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>1.7669</t>
+          <t>2.0568</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0700/--</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>无锡市惠山国有投资控股集团有限公司</t>
+          <t>冀中能源峰峰集团有限公司</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.03</t>
+          <t>C- 23.64</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1453,7 +1447,7 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>09-08 15:00</t>
+          <t>09-08 14:00</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
@@ -1466,18 +1460,16 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="U6" s="4" t="n">
-        <v>3.03</v>
-      </c>
+      <c r="U6" s="3"/>
       <c r="V6" s="3"/>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>2.15%~2.25%</t>
+          <t>2.67%~2.77%</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
@@ -1488,23 +1480,23 @@
       <c r="Z6" s="3"/>
       <c r="AA6" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>河北省-邯郸市</t>
         </is>
       </c>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,仅用于偿还回售的公司债券本金[23惠控02]</t>
+          <t>本期债务融资工具募集资金不超过10.00亿元,拟用于偿还发行人合并范围内金融机构借款。</t>
         </is>
       </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
-          <t>天风证券股份有限公司,国联民生证券承销保荐有限公司</t>
+          <t>光大证券股份有限公司,国金证券股份有限公司</t>
         </is>
       </c>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF6" s="3" t="inlineStr">
@@ -1514,28 +1506,28 @@
       </c>
       <c r="AG6" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH6" s="3" t="inlineStr">
         <is>
-          <t>无锡市惠山国有投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
+          <t>冀中能源峰峰集团有限公司2026年度第二期中期票据(品种二)(取消发行)</t>
         </is>
       </c>
       <c r="AI6" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="inlineStr">
         <is>
-          <t>2033-09-09</t>
+          <t>2031-09-09</t>
         </is>
       </c>
       <c r="AK6" s="3"/>
       <c r="AL6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AM6" s="3" t="inlineStr">
@@ -1550,32 +1542,32 @@
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP6" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ6" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>煤炭采掘</t>
         </is>
       </c>
       <c r="AT6" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU6" s="3" t="inlineStr">
@@ -1603,22 +1595,24 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="AZ6" s="3"/>
+      <c r="AZ6" s="4" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>26冀中峰峰MTN002B(取消发行)</t>
+          <t>26博融02</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>09-08 18:00</t>
+          <t>09-08 19:00</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>DY102683553.IB</t>
+          <t>283817.SH</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1627,49 +1621,55 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F7" s="3"/>
+        <v>8.67</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>8.67</v>
+      </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2.20 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+          <t>1.90 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>77.28</v>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>25冀中峰峰MTN005</t>
+          <t>26博融01</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>1.29Y</t>
+          <t>4.88Y</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>2.0568</t>
+          <t>2.1628</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>2.0700/--</t>
+          <t>2.2000/2.1500</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>冀中能源峰峰集团有限公司</t>
+          <t>江苏博融农业发展有限公司</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>C- 23.64</t>
+          <t>C- 18.42</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>09-08 14:00</t>
+          <t>09-08 15:00</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
@@ -1689,46 +1689,52 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U7" s="3"/>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="n">
+        <v>3.1257</v>
+      </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>2.67%~2.77%</t>
+          <t>2.17%~2.27%</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3" t="inlineStr">
         <is>
-          <t>河北省-邯郸市</t>
+          <t>江苏省-徐州市</t>
         </is>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具募集资金不超过10.00亿元,拟用于偿还发行人合并范围内金融机构借款。</t>
+          <t>本期公司债券发行金额不超过8.67亿元(含8.67亿元)，募集资金扣除发行费用后，全部用于偿还到期公司债券本金[23 博融02]</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司,国金证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD7" s="3"/>
+          <t>国泰海通证券股份有限公司,天风证券股份有限公司,东吴证券股份有限公司,国联民生证券承销保荐有限公司,湘财证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr">
+        <is>
+          <t>江苏润鑫城市投资集团有限公司</t>
+        </is>
+      </c>
       <c r="AE7" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF7" s="3" t="inlineStr">
@@ -1738,68 +1744,68 @@
       </c>
       <c r="AG7" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH7" s="3" t="inlineStr">
         <is>
-          <t>冀中能源峰峰集团有限公司2026年度第二期中期票据(品种二)(取消发行)</t>
+          <t>江苏博融农业发展有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI7" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ7" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
+          <t>2031-09-10</t>
         </is>
       </c>
       <c r="AK7" s="3"/>
       <c r="AL7" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AM7" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ7" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>煤炭采掘</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT7" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU7" s="3" t="inlineStr">
@@ -1809,7 +1815,7 @@
       </c>
       <c r="AV7" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW7" s="3" t="inlineStr">
@@ -1827,14 +1833,12 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="AZ7" s="4" t="n">
-        <v>0.03</v>
-      </c>
+      <c r="AZ7" s="3"/>
     </row>
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26博融02</t>
+          <t>26华发03</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1844,64 +1848,64 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>283817.SH</t>
+          <t>283215.SH</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>1+1+1</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>8.67</v>
+        <v>20.0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>8.67</v>
+        <v>19.0</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.80</t>
+          <t>2.60 ~ 3.15</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2.18</v>
+        <v>3.15</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>77.28</v>
+        <v>189.94</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>26博融01</t>
+          <t>25华发06</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>4.88Y</t>
+          <t>1.12Y+3.00Y</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>2.1628</t>
+          <t>3.3189</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>2.2000/2.1500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>江苏博融农业发展有限公司</t>
+          <t>珠海华发实业股份有限公司</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>C- 18.42</t>
+          <t>B- 35.07</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1921,47 +1925,47 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U8" s="4" t="n">
-        <v>3.1257</v>
+        <v>1.0</v>
       </c>
       <c r="V8" s="3"/>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>2.17%~2.27%</t>
+          <t>2.60%~2.70%</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>江苏省-徐州市</t>
+          <t>广东省-珠海市</t>
         </is>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券发行金额不超过8.67亿元(含8.67亿元)，募集资金扣除发行费用后，全部用于偿还到期公司债券本金[23 博融02]</t>
+          <t>本期公司债券发行规模为不超过20.00亿元(含20.00亿元),募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金以及置换到期的公司债券本金。[23华发04,21华发03]</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,天风证券股份有限公司,东吴证券股份有限公司,国联民生证券承销保荐有限公司,湘财证券股份有限公司</t>
+          <t>华金证券股份有限公司,西部证券股份有限公司,国泰海通证券股份有限公司,第一创业证券承销保荐有限责任公司,国联民生证券承销保荐有限公司,华福证券股份有限公司</t>
         </is>
       </c>
       <c r="AD8" s="3" t="inlineStr">
         <is>
-          <t>江苏润鑫城市投资集团有限公司</t>
+          <t>珠海华发集团有限公司</t>
         </is>
       </c>
       <c r="AE8" s="3" t="inlineStr">
@@ -1981,7 +1985,7 @@
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>江苏博融农业发展有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>珠海华发实业股份有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
@@ -1991,13 +1995,17 @@
       </c>
       <c r="AJ8" s="3" t="inlineStr">
         <is>
-          <t>2031-09-10</t>
-        </is>
-      </c>
-      <c r="AK8" s="3"/>
+          <t>2029-09-09</t>
+        </is>
+      </c>
+      <c r="AK8" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL8" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AM8" s="3" t="inlineStr">
@@ -2007,42 +2015,42 @@
       </c>
       <c r="AN8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP8" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ8" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>房地产</t>
         </is>
       </c>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>住宅楼房</t>
         </is>
       </c>
       <c r="AT8" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU8" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2027-09-09</t>
         </is>
       </c>
       <c r="AV8" s="3" t="inlineStr">
@@ -2052,7 +2060,7 @@
       </c>
       <c r="AW8" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX8" s="3" t="inlineStr">
@@ -2070,7 +2078,7 @@
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26华发03</t>
+          <t>26中证K3</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2080,64 +2088,64 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>283215.SH</t>
+          <t>246027.SH</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>1+1+1</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>20.0</v>
+        <v>60.0</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>19.0</v>
+        <v>60.0</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2.60 ~ 3.15</t>
+          <t>1.10 ~ 2.10</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.15</v>
+        <v>1.63</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>189.94</v>
+        <v>37.94</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>25华发06</t>
+          <t>26中证14</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>1.12Y+3.00Y</t>
+          <t>2.84Y</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>3.3189</t>
+          <t>1.6179</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6600/--</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>珠海华发实业股份有限公司</t>
+          <t>中信证券股份有限公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>B- 35.07</t>
+          <t>A- 64.81</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2157,21 +2165,21 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.0</v>
+        <v>2.78</v>
       </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>2.60%~2.70%</t>
+          <t>1.59%~1.69%</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
@@ -2179,35 +2187,35 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z9" s="3"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>广东省-珠海市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券发行规模为不超过20.00亿元(含20.00亿元),募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金以及置换到期的公司债券本金。[23华发04,21华发03]</t>
+          <t>本期债券募集资金不低于70%的部分用于专项支持科技创新领域业务,剩余部分用于补充公司流动资金。</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>华金证券股份有限公司,西部证券股份有限公司,国泰海通证券股份有限公司,第一创业证券承销保荐有限责任公司,国联民生证券承销保荐有限公司,华福证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD9" s="3" t="inlineStr">
-        <is>
-          <t>珠海华发集团有限公司</t>
-        </is>
-      </c>
+          <t>广发证券股份有限公司,平安证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG9" s="3" t="inlineStr">
@@ -2217,27 +2225,23 @@
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>珠海华发实业股份有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>中信证券股份有限公司2026年面向专业机构投资者公开发行科技创新公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
-        </is>
-      </c>
-      <c r="AK9" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-10</t>
+        </is>
+      </c>
+      <c r="AK9" s="3"/>
       <c r="AL9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t/>
         </is>
       </c>
       <c r="AM9" s="3" t="inlineStr">
@@ -2247,52 +2251,52 @@
       </c>
       <c r="AN9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ9" s="3" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>住宅楼房</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT9" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU9" s="3" t="inlineStr">
         <is>
-          <t>2027-09-09</t>
+          <t/>
         </is>
       </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW9" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX9" s="3" t="inlineStr">
@@ -2310,7 +2314,7 @@
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26中证K3</t>
+          <t>26越产03</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2320,64 +2324,64 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>246027.SH</t>
+          <t>524994.SZ</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>60.0</v>
+        <v>5.0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>60.0</v>
+        <v>5.0</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>37.94</v>
+        <v>40.28</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26中证14</t>
+          <t>26越秀产投MTN001(科创债)</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>2.84Y</t>
+          <t>4.91Y</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.6179</t>
+          <t>1.9112</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>1.6600/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司</t>
+          <t>广州越秀产业投资有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>A- 64.81</t>
+          <t>C 28.20</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2387,7 +2391,7 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>09-08 15:00</t>
+          <t>09-08 16:00</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
@@ -2401,63 +2405,63 @@
         </is>
       </c>
       <c r="U10" s="4" t="n">
-        <v>2.78</v>
+        <v>4.16</v>
       </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X10" s="3" t="inlineStr">
-        <is>
-          <t>1.59%~1.69%</t>
-        </is>
-      </c>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X10" s="3"/>
       <c r="Y10" s="3" t="inlineStr">
         <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金不低于70%的部分用于专项支持科技创新领域业务,剩余部分用于补充公司流动资金。</t>
+          <t>本期公司债券的募集资金扣除发行费用后拟用于偿付到期公司债券本金[23越产03]</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>广发证券股份有限公司,平安证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD10" s="3"/>
+          <t>中信证券股份有限公司,华泰联合证券有限责任公司,广发证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr">
+        <is>
+          <t>广州越秀集团股份有限公司,广州越秀资本控股集团股份有限公司</t>
+        </is>
+      </c>
       <c r="AE10" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG10" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司2026年面向专业机构投资者公开发行科技创新公司债券(第三期)</t>
+          <t>广州越秀产业投资有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2467,7 +2471,7 @@
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2029-09-10</t>
+          <t>2031-09-10</t>
         </is>
       </c>
       <c r="AK10" s="3"/>
@@ -2491,11 +2495,7 @@
           <t>金融</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
+      <c r="AP10" s="3"/>
       <c r="AQ10" s="3" t="inlineStr">
         <is>
           <t>非银</t>
@@ -2503,17 +2503,17 @@
       </c>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW10" s="3" t="inlineStr">
@@ -2546,7 +2546,7 @@
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26越产03</t>
+          <t>26城建K2</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>524994.SZ</t>
+          <t>245938.SH</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -2565,21 +2565,21 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>5.0</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.25 ~ 2.25</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>40.28</v>
+        <v>29.28</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>26越秀产投MTN001(科创债)</t>
+          <t>24京城建MTN004</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>4.91Y</t>
+          <t>3.19Y</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.9112</t>
+          <t>1.7013</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7000</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>广州越秀产业投资有限公司</t>
+          <t>北京城建集团有限责任公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>C 28.20</t>
+          <t>C- 22.01</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2637,45 +2637,37 @@
         </is>
       </c>
       <c r="U11" s="4" t="n">
-        <v>4.16</v>
+        <v>4.6</v>
       </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X11" s="3"/>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z11" s="3" t="inlineStr">
-        <is>
           <t>AAA</t>
         </is>
       </c>
+      <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券的募集资金扣除发行费用后拟用于偿付到期公司债券本金[23越产03]</t>
+          <t>本期债券发行金额为不超过18亿元(含18亿元)，募集资金拟用于生产性支出,包括偿还公司债务、补充公司流动资金等符合法律法规要求的用途。</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,华泰联合证券有限责任公司,广发证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD11" s="3" t="inlineStr">
-        <is>
-          <t>广州越秀集团股份有限公司,广州越秀资本控股集团股份有限公司</t>
-        </is>
-      </c>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,招商证券股份有限公司,国信证券股份有限公司,首创证券股份有限公司,第一创业证券承销保荐有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD11" s="3"/>
       <c r="AE11" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -2688,12 +2680,12 @@
       </c>
       <c r="AG11" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>广州越秀产业投资有限公司2026年面向专业投资者公开发行公司债券(第三期)</t>
+          <t>北京城建集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
@@ -2714,7 +2706,7 @@
       </c>
       <c r="AM11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AN11" s="3" t="inlineStr">
@@ -2724,28 +2716,32 @@
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP11" s="3"/>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>房屋建筑</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>其他房建</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
@@ -2755,7 +2751,7 @@
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW11" s="3" t="inlineStr">
@@ -2778,7 +2774,7 @@
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26城建K2</t>
+          <t>26晋桥K1</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2788,7 +2784,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>245938.SH</t>
+          <t>524980.SZ</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -2797,55 +2793,55 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="F12" s="4" t="n">
         <v>5.0</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.25 ~ 2.25</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.7</v>
+        <v>1.97</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>29.28</v>
+        <v>56.28</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>24京城建MTN004</t>
+          <t>26晋路桥MTN002</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>3.19Y</t>
+          <t>2.64Y</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.7013</t>
+          <t>1.8727</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>--/1.7000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>北京城建集团有限责任公司</t>
+          <t>山西路桥建设集团有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C- 22.01</t>
+          <t>C 27.77</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2855,7 +2851,7 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>09-08 16:00</t>
+          <t>09-08 15:00</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
@@ -2869,15 +2865,19 @@
         </is>
       </c>
       <c r="U12" s="4" t="n">
-        <v>4.6</v>
+        <v>2.57</v>
       </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X12" s="3"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>2.10%~2.20%</t>
+        </is>
+      </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -2886,17 +2886,17 @@
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>山西省</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行金额为不超过18亿元(含18亿元)，募集资金拟用于生产性支出,包括偿还公司债务、补充公司流动资金等符合法律法规要求的用途。</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还有息负债</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,招商证券股份有限公司,国信证券股份有限公司,首创证券股份有限公司,第一创业证券承销保荐有限责任公司</t>
+          <t>五矿证券有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD12" s="3"/>
@@ -2912,12 +2912,12 @@
       </c>
       <c r="AG12" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>北京城建集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第一期)(品种二)</t>
+          <t>山西路桥建设集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="AM12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AN12" s="3" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="AP12" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ12" s="3" t="inlineStr">
@@ -2963,17 +2963,17 @@
       </c>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>房屋建筑</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>其他房建</t>
+          <t>市政路桥</t>
         </is>
       </c>
       <c r="AT12" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU12" s="3" t="inlineStr">
@@ -3006,74 +3006,74 @@
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26晋桥K1</t>
+          <t>26建投新能MTN003</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>09-08 19:00</t>
+          <t>09-08 18:00</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>524980.SZ</t>
+          <t>102683548.IB</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.60 ~ 1.90</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.97</v>
+        <v>1.73</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>56.28</v>
+        <v>47.94</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>26晋路桥MTN002</t>
+          <t>26建投新能MTN002</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>2.64Y</t>
+          <t>1.91Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.8727</t>
+          <t>1.6546</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6000</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>山西路桥建设集团有限公司</t>
+          <t>河北建投新能源有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>C 27.77</t>
+          <t>C- 24.35</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>09-08 15:00</t>
+          <t>09-08 09:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -3093,48 +3093,50 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U13" s="4" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="V13" s="3"/>
+        <v>3.6333</v>
+      </c>
+      <c r="V13" s="4" t="n">
+        <v>1.04</v>
+      </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>2.10%~2.20%</t>
+          <t>1.70%~1.80%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>山西省</t>
+          <t>河北省-石家庄市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还有息负债</t>
+          <t>本期发行6亿元中期票据募集资金拟全部用于偿还发行人2025年度第五期超短期融资券有息债务本金[25建投新能SCP005]</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>五矿证券有限公司,中国国际金融股份有限公司,中信证券股份有限公司</t>
+          <t>中国建设银行股份有限公司,国家开发银行</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
@@ -3144,12 +3146,12 @@
       </c>
       <c r="AG13" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>山西路桥建设集团有限公司2026年面向专业投资者公开发行科技创新公司债券(第一期)</t>
+          <t>河北建投新能源有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -3159,23 +3161,27 @@
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2031-09-10</t>
-        </is>
-      </c>
-      <c r="AK13" s="3"/>
+          <t>2029-09-09</t>
+        </is>
+      </c>
+      <c r="AK13" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL13" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AM13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AO13" s="3" t="inlineStr">
@@ -3185,27 +3191,27 @@
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>市政路桥</t>
+          <t>风电</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
@@ -3238,7 +3244,7 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26建投新能MTN003</t>
+          <t>26夏商SCP023</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3248,64 +3254,64 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>102683548.IB</t>
+          <t>012682219.IB</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.16Y</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 1.90</t>
+          <t>1.30 ~ 1.49</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>47.94</v>
+        <v>30.9</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>26建投新能MTN002</t>
+          <t>26夏商SCP022</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>1.91Y</t>
+          <t>52D</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.6546</t>
+          <t>1.4898</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/1.6000</t>
+          <t>1.5200/1.5000</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>河北建投新能源有限公司</t>
+          <t>厦门夏商集团有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C- 24.35</t>
+          <t>C+ 30.38</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3329,19 +3335,19 @@
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>3.6333</v>
+        <v>0.48</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>1.04</v>
+        <v>1.0</v>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.70%~1.80%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -3352,23 +3358,23 @@
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>河北省-石家庄市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期发行6亿元中期票据募集资金拟全部用于偿还发行人2025年度第五期超短期融资券有息债务本金[25建投新能SCP005]</t>
+          <t>发行人本期发行超短期融资券5亿元，扣除承销费后，拟全部用于偿还发行人本部银行借款。</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,国家开发银行</t>
+          <t>交通银行股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
@@ -3383,7 +3389,7 @@
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>河北建投新能源有限公司2026年度第三期中期票据</t>
+          <t>厦门夏商集团有限公司2026年度第二十三期超短期融资券</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3393,14 +3399,10 @@
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
-        </is>
-      </c>
-      <c r="AK14" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="AK14" s="3"/>
       <c r="AL14" s="3" t="inlineStr">
         <is>
           <t>2026-09-10</t>
@@ -3408,7 +3410,7 @@
       </c>
       <c r="AM14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AN14" s="3" t="inlineStr">
@@ -3423,27 +3425,27 @@
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>风电</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3476,7 +3478,7 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP023</t>
+          <t>26晋陵投资MTN002</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3486,12 +3488,12 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>012682219.IB</t>
+          <t>102683550.IB</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>0.16Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
@@ -3502,48 +3504,48 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.49</t>
+          <t>1.60 ~ 2.20</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.49</v>
+        <v>1.81</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>30.9</v>
+        <v>40.28</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP022</t>
+          <t>26晋陵投资MTN001</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>52D</t>
+          <t>4.95Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.4898</t>
+          <t>1.9095</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>1.5200/1.5000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司</t>
+          <t>常州市晋陵投资集团有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.38</t>
+          <t>C- 21.62</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3567,19 +3569,19 @@
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.48</v>
+        <v>4.44</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.0</v>
+        <v>1.064</v>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
@@ -3590,23 +3592,23 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>江苏省-常州市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行超短期融资券5亿元，扣除承销费后，拟全部用于偿还发行人本部银行借款。</t>
+          <t>发行人本期中期票据发行金额为5亿元,用于归还发行人债务融资工具本金[23晋陵投资MTN002]</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>交通银行股份有限公司</t>
+          <t>中信银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -3621,7 +3623,7 @@
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司2026年度第二十三期超短期融资券</t>
+          <t>常州市晋陵投资集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3631,7 +3633,7 @@
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2026-11-06</t>
+          <t>2031-09-09</t>
         </is>
       </c>
       <c r="AK15" s="3"/>
@@ -3652,7 +3654,7 @@
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP15" s="3" t="inlineStr">
@@ -3662,22 +3664,22 @@
       </c>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
@@ -3710,7 +3712,7 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26晋陵投资MTN002</t>
+          <t>26天成租赁SCP026</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3720,64 +3722,64 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>102683550.IB</t>
+          <t>012682218.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.37Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.20</t>
+          <t>1.30 ~ 1.49</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.81</v>
+        <v>1.49</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>40.28</v>
+        <v>25.87</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26晋陵投资MTN001</t>
+          <t>26天成租赁SCP025</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>4.95Y</t>
+          <t>129D</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.9095</t>
+          <t>1.5024</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5200/1.5000</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>常州市晋陵投资集团有限公司</t>
+          <t>华能天成融资租赁有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C- 21.62</t>
+          <t>C 26.46</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3801,51 +3803,49 @@
         </is>
       </c>
       <c r="U16" s="4" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="V16" s="4" t="n">
-        <v>1.064</v>
-      </c>
+        <v>0.43</v>
+      </c>
+      <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>江苏省-常州市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额为5亿元,用于归还发行人债务融资工具本金[23晋陵投资MTN002]</t>
+          <t>本期债务融资工具全部募集资金拟用于偿还到期的债务融资工具,保障资金周转[26天成租赁SCP022]</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,兴业银行股份有限公司</t>
+          <t>北京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG16" s="3" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>常州市晋陵投资集团有限公司2026年度第二期中期票据</t>
+          <t>华能天成融资租赁有限公司2026年度第二十六期超短期融资券</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3865,7 +3865,7 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
+          <t>2027-01-22</t>
         </is>
       </c>
       <c r="AK16" s="3"/>
@@ -3886,32 +3886,32 @@
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP16" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3944,7 +3944,7 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26天成租赁SCP026</t>
+          <t>26赣建工MTN001</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3954,64 +3954,64 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>012682218.IB</t>
+          <t>102683554.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>0.37Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.49</t>
+          <t>1.80 ~ 2.47</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.49</v>
+        <v>2.47</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>25.87</v>
+        <v>106.28</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>26天成租赁SCP025</t>
+          <t>24赣建工MTN001B</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>129D</t>
+          <t>2.92Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.5024</t>
+          <t>2.5038</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>1.5200/1.5000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>华能天成融资租赁有限公司</t>
+          <t>江西省建工集团有限责任公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C 26.46</t>
+          <t>B- 41.60</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4035,49 +4035,49 @@
         </is>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.43</v>
+        <v>0.22</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>2.72%~2.82%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>江西省</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具全部募集资金拟用于偿还到期的债务融资工具,保障资金周转[26天成租赁SCP022]</t>
+          <t>发行人本期中期票据发行规模5亿元，募集资金拟全部用于偿还发行人本部有息债务。</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>北京银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,北京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG17" s="3" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>华能天成融资租赁有限公司2026年度第二十六期超短期融资券</t>
+          <t>江西省建工集团有限责任公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2027-01-22</t>
+          <t>2031-09-09</t>
         </is>
       </c>
       <c r="AK17" s="3"/>
@@ -4118,37 +4118,37 @@
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-09</t>
         </is>
       </c>
       <c r="AV17" s="3" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX17" s="3" t="inlineStr">
@@ -4176,74 +4176,70 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26赣建工MTN001</t>
+          <t>26中信建投CP016</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>09-08 18:00</t>
+          <t>09-08 17:00</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>102683554.IB</t>
+          <t>072610177.IB</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>0.52Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>5.0</v>
+        <v>30.0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>1.80 ~ 2.47</t>
-        </is>
-      </c>
+        <v>30.0</v>
+      </c>
+      <c r="G18" s="3"/>
       <c r="H18" s="4" t="n">
-        <v>2.47</v>
+        <v>1.5</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>106.28</v>
+        <v>26.79</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>24赣建工MTN001B</t>
+          <t>26中信建投CP015</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>2.92Y</t>
+          <t>171D</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>2.5038</t>
+          <t>1.4828</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4800</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>江西省建工集团有限责任公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>B- 41.60</t>
+          <t>B- 42.80</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4266,50 +4262,44 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="U18" s="4" t="n">
-        <v>0.22</v>
-      </c>
+      <c r="U18" s="3"/>
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>2.72%~2.82%</t>
+          <t>1.45%~1.49%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>江西省</t>
-        </is>
-      </c>
-      <c r="AB18" s="3" t="inlineStr">
-        <is>
-          <t>发行人本期中期票据发行规模5亿元，募集资金拟全部用于偿还发行人本部有息债务。</t>
-        </is>
-      </c>
+          <t>北京市</t>
+        </is>
+      </c>
+      <c r="AB18" s="3"/>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,北京银行股份有限公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>证券公司短期融资券</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG18" s="3" t="inlineStr">
@@ -4319,7 +4309,7 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>江西省建工集团有限责任公司2026年度第一期中期票据</t>
+          <t>中信建投证券股份有限公司2026年度第十六期短期融资券</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4329,7 +4319,7 @@
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2031-09-09</t>
+          <t>2027-03-19</t>
         </is>
       </c>
       <c r="AK18" s="3"/>
@@ -4340,7 +4330,7 @@
       </c>
       <c r="AM18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AN18" s="3" t="inlineStr">
@@ -4350,37 +4340,37 @@
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
+          <t/>
         </is>
       </c>
       <c r="AV18" s="3" t="inlineStr">
@@ -4390,7 +4380,7 @@
       </c>
       <c r="AW18" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX18" s="3" t="inlineStr">
@@ -4408,70 +4398,74 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26中信建投CP016</t>
+          <t>26晋江城投MTN001</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>09-08 17:00</t>
+          <t>09-08 18:00</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>072610177.IB</t>
+          <t>102683555.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>0.52Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>30.0</v>
+        <v>4.2</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>30.0</v>
-      </c>
-      <c r="G19" s="3"/>
+        <v>8.7</v>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>1.40 ~ 2.20</t>
+        </is>
+      </c>
       <c r="H19" s="4" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>26.79</v>
+        <v>46.94</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26中信建投CP015</t>
+          <t>24晋江城投MTN001</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>171D</t>
+          <t>2.94Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.4828</t>
+          <t>1.7251</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>--/1.4800</t>
+          <t>1.7600/1.7000</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>福建省晋江城市建设投资开发集团有限责任公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>B- 42.80</t>
+          <t>B- 36.00</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4494,44 +4488,52 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
+      <c r="U19" s="4" t="n">
+        <v>4.023</v>
+      </c>
+      <c r="V19" s="4" t="n">
+        <v>1.869</v>
+      </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.45%~1.49%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
-        </is>
-      </c>
-      <c r="AB19" s="3"/>
+          <t>福建省-泉州市</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>本期中期票据发行8.70亿元,拟用于偿还债务融资工具本金。[25晋江城投SCP003B]</t>
+        </is>
+      </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>中信银行股份有限公司,国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>证券公司短期融资券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG19" s="3" t="inlineStr">
@@ -4541,7 +4543,7 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司2026年度第十六期短期融资券</t>
+          <t>福建省晋江城市建设投资开发集团有限责任公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4551,10 +4553,14 @@
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2027-03-19</t>
-        </is>
-      </c>
-      <c r="AK19" s="3"/>
+          <t>2029-09-09</t>
+        </is>
+      </c>
+      <c r="AK19" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL19" s="3" t="inlineStr">
         <is>
           <t>2026-09-10</t>
@@ -4562,42 +4568,42 @@
       </c>
       <c r="AM19" s="3" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>综合基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
@@ -4630,7 +4636,7 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26晋江城投MTN001</t>
+          <t>26安吉租赁MTN003</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4640,7 +4646,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>102683555.IB</t>
+          <t>102683565.IB</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -4649,55 +4655,55 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>4.2</v>
+        <v>3.0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>8.7</v>
+        <v>3.0</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.20</t>
+          <t>1.60 ~ 1.80</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>46.94</v>
+        <v>54.94</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>24晋江城投MTN001</t>
+          <t>26安吉租赁MTN002</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>2.94Y</t>
+          <t>2.92Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.7251</t>
+          <t>1.7928</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>1.7600/1.7000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>福建省晋江城市建设投资开发集团有限责任公司</t>
+          <t>安吉租赁有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>B- 36.00</t>
+          <t>C 28.81</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4721,19 +4727,19 @@
         </is>
       </c>
       <c r="U20" s="4" t="n">
-        <v>4.023</v>
+        <v>0.9667</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>1.869</v>
+        <v>1.0</v>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -4744,17 +4750,17 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>福建省-泉州市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行8.70亿元,拟用于偿还债务融资工具本金。[25晋江城投SCP003B]</t>
+          <t>本期中期票据发行规模为3亿元,全部用于偿还发行人的银行借款</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,国信证券股份有限公司</t>
+          <t>江苏银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
@@ -4775,7 +4781,7 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>福建省晋江城市建设投资开发集团有限责任公司2026年度第一期中期票据</t>
+          <t>安吉租赁有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4810,32 +4816,32 @@
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>综合基础设施投融资建设</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4868,7 +4874,7 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26安吉租赁MTN003</t>
+          <t>26合川城投PPN006</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4878,7 +4884,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>102683565.IB</t>
+          <t>032690017.IB</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -4887,40 +4893,40 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 1.80</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>54.94</v>
+        <v>53.94</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26安吉租赁MTN002</t>
+          <t>24渝合02</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>2.92Y</t>
+          <t>2.98Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.7928</t>
+          <t>1.8548</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -4930,12 +4936,12 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>安吉租赁有限公司</t>
+          <t>重庆市合川城市建设投资(集团)有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C 28.81</t>
+          <t>C- 17.70</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4959,19 +4965,19 @@
         </is>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.9667</v>
+        <v>5.35</v>
       </c>
       <c r="V21" s="4" t="n">
         <v>1.0</v>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.87%~1.97%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
@@ -4982,23 +4988,23 @@
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>重庆市-合川区</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模为3亿元,全部用于偿还发行人的银行借款</t>
+          <t>发行人本次定向工具注册额度为30亿元,本期债务融资工具基础发行规模为0亿元,发行规模上限为2亿元。资金全部用于偿还公司存续的债务融资工具[23合川城投MTN004B]</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>重庆银行股份有限公司,中泰证券股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
@@ -5013,12 +5019,12 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>安吉租赁有限公司2026年度第三期中期票据</t>
+          <t>重庆市合川城市建设投资(集团)有限公司2026年度第六期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ21" s="3" t="inlineStr">
@@ -5048,32 +5054,32 @@
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -5106,166 +5112,172 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26大同D2</t>
+          <t>26中电金投MTN002(并购)</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>09-08 17:00</t>
+          <t>09-08 18:00</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>283781.SH</t>
+          <t>102683563.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>0.48Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>47.94</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>26金投K1</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>2.72Y</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>1.6933</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>中电金投控股有限公司</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>B- 42.03</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>09-08 09:00</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T22" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="U22" s="4" t="n">
+        <v>2.6923</v>
+      </c>
+      <c r="V22" s="4" t="n">
         <v>2.0</v>
       </c>
-      <c r="F22" s="4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>1.80 ~ 2.09</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>85.79</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>25大同D1</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>52D</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>2.6629</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>大同证券有限责任公司</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="inlineStr">
-        <is>
-          <t>C- 10.11</t>
-        </is>
-      </c>
-      <c r="Q22" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="R22" s="3" t="inlineStr">
-        <is>
-          <t>09-08 13:00</t>
-        </is>
-      </c>
-      <c r="S22" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="T22" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U22" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>2.49%~2.53%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>山西省-大同市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模不超过人民币2.00亿元(含2.00亿元)。本期债券募集资金扣除发行费用后,1.50亿元用于偿还到期短期公司债券,剩余部分用于补充流动资金。[26大同D1]</t>
+          <t>本期中期票据基础发行规模为0亿元,发行规模上限为6.50亿元,其中3.0678亿元拟用于偿还到期有息债务,3.36742亿元拟用于置换发行人过去一年内通过大宗交易参股并购武汉达梦数据库股份有限公司(688692.SH)股份所投入的自有资金,置换后的资金及本期债券剩余募集资金拟用于发行人及其子公司偿还有息债务等。[24中电K1]</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>大同证券有限责任公司</t>
+          <t>招商证券股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG22" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>大同证券有限责任公司2026年面向专业投资者非公开发行短期公司债券(第二期)</t>
+          <t>中电金投控股有限公司2026年度第二期中期票据(并购)</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2027-03-03</t>
-        </is>
-      </c>
-      <c r="AK22" s="3"/>
+          <t>2029-09-09</t>
+        </is>
+      </c>
+      <c r="AK22" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AM22" s="3" t="inlineStr">
@@ -5283,11 +5295,7 @@
           <t>金融</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+      <c r="AP22" s="3"/>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
           <t>非银</t>
@@ -5295,17 +5303,17 @@
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5338,7 +5346,7 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26合川城投PPN006</t>
+          <t>26河北高速MTN006</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5348,7 +5356,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>032690017.IB</t>
+          <t>102683549.IB</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -5357,55 +5365,55 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.40 ~ 1.80</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.79</v>
+        <v>1.58</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>53.94</v>
+        <v>32.94</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>24渝合02</t>
+          <t>26河北高速MTN005</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>2.98Y</t>
+          <t>2.93Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.8548</t>
+          <t>1.6698</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6800/1.6400</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>重庆市合川城市建设投资(集团)有限公司</t>
+          <t>河北高速公路集团有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>C- 17.70</t>
+          <t>C 25.60</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5415,7 +5423,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>09-08 09:00</t>
+          <t>09-08 15:00</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -5429,46 +5437,46 @@
         </is>
       </c>
       <c r="U23" s="4" t="n">
-        <v>5.35</v>
+        <v>4.49</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.0</v>
+        <v>1.18</v>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.87%~1.97%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>重庆市-合川区</t>
+          <t>河北省</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>发行人本次定向工具注册额度为30亿元,本期债务融资工具基础发行规模为0亿元,发行规模上限为2亿元。资金全部用于偿还公司存续的债务融资工具[23合川城投MTN004B]</t>
+          <t>发行人本期中期票据发行规模为10亿元,期限三年,募集资金拟用于偿还发行人即将到期的有息债务和补充流动资金。</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>重庆银行股份有限公司,中泰证券股份有限公司,华夏银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
@@ -5483,12 +5491,12 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>重庆市合川城市建设投资(集团)有限公司2026年度第六期定向债务融资工具</t>
+          <t>河北高速公路集团有限公司2026年度第六期中期票据</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ23" s="3" t="inlineStr">
@@ -5518,32 +5526,32 @@
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5576,7 +5584,7 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26中电金投MTN002(并购)</t>
+          <t>26冀中峰峰MTN002A</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5586,7 +5594,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>102683563.IB</t>
+          <t>102683552.IB</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -5595,55 +5603,55 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>6.5</v>
+        <v>8.0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6.5</v>
+        <v>8.0</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>2.00 ~ 2.80</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.73</v>
+        <v>2.45</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>47.94</v>
+        <v>119.94</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26金投K1</t>
+          <t>25冀中峰峰MTN005</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>2.72Y</t>
+          <t>1.29Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.6933</t>
+          <t>2.0568</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0700/--</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>中电金投控股有限公司</t>
+          <t>冀中能源峰峰集团有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>B- 42.03</t>
+          <t>C- 23.64</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5653,7 +5661,7 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>09-08 09:00</t>
+          <t>09-08 14:00</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -5667,40 +5675,40 @@
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>2.6923</v>
+        <v>1.6875</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>2.0</v>
+        <v>1.1</v>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>2.30%~2.40%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>河北省-邯郸市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据基础发行规模为0亿元,发行规模上限为6.50亿元,其中3.0678亿元拟用于偿还到期有息债务,3.36742亿元拟用于置换发行人过去一年内通过大宗交易参股并购武汉达梦数据库股份有限公司(688692.SH)股份所投入的自有资金,置换后的资金及本期债券剩余募集资金拟用于发行人及其子公司偿还有息债务等。[24中电K1]</t>
+          <t>本期债务融资工具募集资金不超过10.00亿元,拟用于偿还发行人合并范围内金融机构借款。</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>招商证券股份有限公司,中国建设银行股份有限公司</t>
+          <t>光大证券股份有限公司,国金证券股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
@@ -5711,7 +5719,7 @@
       </c>
       <c r="AF24" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG24" s="3" t="inlineStr">
@@ -5721,7 +5729,7 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>中电金投控股有限公司2026年度第二期中期票据(并购)</t>
+          <t>冀中能源峰峰集团有限公司2026年度第二期中期票据(品种一)</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5756,28 +5764,32 @@
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP24" s="3"/>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>煤炭采掘</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5810,17 +5822,17 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26河北高速MTN006</t>
+          <t>26东莞银行债01</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>09-08 18:00</t>
+          <t>09-08 16:15</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>102683549.IB</t>
+          <t>212680037.IB</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -5829,55 +5841,55 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>10.0</v>
+        <v>45.0</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.80</t>
+          <t>1.30 ~ 1.90</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>32.94</v>
+        <v>35.94</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>26河北高速MTN005</t>
+          <t>25东莞银行科创债(柜台)</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>2.93Y</t>
+          <t>3.78Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.6698</t>
+          <t>1.5906</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>1.6800/1.6400</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>河北高速公路集团有限公司</t>
+          <t>东莞银行股份有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C 25.60</t>
+          <t>B+ 55.33</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5887,7 +5899,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>09-08 15:00</t>
+          <t>09-08 09:00</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -5897,23 +5909,19 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="U25" s="4" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="V25" s="4" t="n">
-        <v>1.18</v>
-      </c>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="U25" s="3"/>
+      <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.57%~1.67%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
@@ -5924,23 +5932,23 @@
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>河北省</t>
+          <t>广东省-东莞市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行规模为10亿元,期限三年,募集资金拟用于偿还发行人即将到期的有息债务和补充流动资金。</t>
+          <t>本期债券募集资金补充中长期稳定资金，提高核心负债规模，并响应东莞市构建“8+8+4”现代化产业体系需要，资金用于支持东莞区域产业信贷投放。</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中国光大银行股份有限公司</t>
+          <t>中国国际金融股份有限公司,兴业银行股份有限公司,华夏银行股份有限公司,国泰海通证券股份有限公司,中国邮政储蓄银行股份有限公司,中信证券股份有限公司,中国银河证券股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
       <c r="AE25" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF25" s="3" t="inlineStr">
@@ -5955,7 +5963,7 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>河北高速公路集团有限公司2026年度第六期中期票据</t>
+          <t>东莞银行股份有限公司2026年金融债券(第一期)</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5965,32 +5973,28 @@
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
-        </is>
-      </c>
-      <c r="AK25" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-10</t>
+        </is>
+      </c>
+      <c r="AK25" s="3"/>
       <c r="AL25" s="3" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AM25" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP25" s="3" t="inlineStr">
@@ -6000,22 +6004,22 @@
       </c>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -6048,74 +6052,74 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26冀中峰峰MTN002A</t>
+          <t>26湘建K4</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>09-08 18:00</t>
+          <t>09-08 19:00</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>102683552.IB</t>
+          <t>246019.SH</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.80</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>2.45</v>
+        <v>2.02</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>119.94</v>
+        <v>61.28</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>25冀中峰峰MTN005</t>
+          <t>26湘建K3</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>1.29Y</t>
+          <t>4.79Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>2.0568</t>
+          <t>2.0303</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>2.0700/--</t>
+          <t>2.0200/2.0100</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>冀中能源峰峰集团有限公司</t>
+          <t>湖南建设投资集团有限责任公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C- 23.64</t>
+          <t>C+ 30.76</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6125,7 +6129,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>09-08 14:00</t>
+          <t>09-08 15:00</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -6135,50 +6139,48 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="U26" s="4" t="n">
-        <v>1.6875</v>
-      </c>
-      <c r="V26" s="4" t="n">
-        <v>1.1</v>
-      </c>
+        <v>3.2429</v>
+      </c>
+      <c r="V26" s="3"/>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>2.30%~2.40%</t>
+          <t>1.97%~2.07%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>河北省-邯郸市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具募集资金不超过10.00亿元,拟用于偿还发行人合并范围内金融机构借款。</t>
+          <t>本期债券募集资金扣除发行费用后,拟用于生产性支出,包括偿还债务、补充流动资金、项目建设等</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>光大证券股份有限公司,国金证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,财信证券股份有限公司,华泰联合证券有限责任公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
@@ -6188,12 +6190,12 @@
       </c>
       <c r="AG26" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>冀中能源峰峰集团有限公司2026年度第二期中期票据(品种一)</t>
+          <t>湖南建设投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6203,29 +6205,25 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2029-09-09</t>
-        </is>
-      </c>
-      <c r="AK26" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-10</t>
+        </is>
+      </c>
+      <c r="AK26" s="3"/>
       <c r="AL26" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AM26" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
           <t>产业</t>
@@ -6233,27 +6231,27 @@
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>煤炭采掘</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
@@ -6286,17 +6284,17 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26东莞银行债01</t>
+          <t>26重庆银行绿债01</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>09-08 16:15</t>
+          <t>09-08 18:00</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>212680037.IB</t>
+          <t>222680021.IB</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -6305,40 +6303,40 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>25.0</v>
+        <v>50.0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>45.0</v>
+        <v>50.0</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.90</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>35.94</v>
+        <v>33.94</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>25东莞银行科创债(柜台)</t>
+          <t>24重庆银行绿色债01(柜台)</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>3.78Y</t>
+          <t>264D</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.5906</t>
+          <t>1.4794</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -6348,12 +6346,12 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>东莞银行股份有限公司</t>
+          <t>重庆银行股份有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>B+ 55.33</t>
+          <t>B+ 57.32</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6376,16 +6374,18 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="U27" s="3"/>
+      <c r="U27" s="4" t="n">
+        <v>2.58</v>
+      </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.57%~1.67%</t>
+          <t>1.55%~1.65%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
@@ -6393,20 +6393,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z27" s="3"/>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>广东省-东莞市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金补充中长期稳定资金，提高核心负债规模，并响应东莞市构建“8+8+4”现代化产业体系需要，资金用于支持东莞区域产业信贷投放。</t>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准,用于《绿色金融支持项目目录(2025年版)》规定的绿色产业项目,优先投向符合《多边可持续金融共同分类目录》的绿色产业项目；重庆银行2026年绿色金融债券(第一期)募集资金拟投放绿色产业项目14个,金额合计人民币50.06亿元；本期债券募集资金应全部用于支持绿色项目的发展,可以直接将绿色金融债券募集资金用于发放绿色项目贷款,闲置资金也可以投资于非金融企业发行的绿色债券以及具有良好信用等级和市场流动性的货币市场工具；确保在债券存续期内,募集资金全部用于绿色项目贷款[重庆银行2026年绿色金融债券(第一期)]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,兴业银行股份有限公司,华夏银行股份有限公司,国泰海通证券股份有限公司,中国邮政储蓄银行股份有限公司,中信证券股份有限公司,中国银河证券股份有限公司,中国建设银行股份有限公司</t>
+          <t>中国国际金融股份有限公司,中国邮政储蓄银行股份有限公司,国投证券股份有限公司,国泰海通证券股份有限公司,江苏银行股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司,中国银行股份有限公司,国开证券股份有限公司,中国银河证券股份有限公司,西南证券股份有限公司,中银国际证券股份有限公司,东方证券股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
@@ -6427,7 +6431,7 @@
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>东莞银行股份有限公司2026年金融债券(第一期)</t>
+          <t>重庆银行股份有限公司2026年绿色金融债券(第一期)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
@@ -6516,7 +6520,7 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26湘建K4</t>
+          <t>26中财G9</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6526,64 +6530,64 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>246019.SH</t>
+          <t>246022.SH</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>7.0</v>
+        <v>22.0</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2.02</v>
+        <v>1.67</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>61.28</v>
+        <v>41.94</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>26湘建K3</t>
+          <t>26中财G7</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>4.79Y</t>
+          <t>2.79Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>2.0303</t>
+          <t>1.6629</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>2.0200/2.0100</t>
+          <t>1.6650/1.6500</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>湖南建设投资集团有限责任公司</t>
+          <t>中国中金财富证券有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.76</t>
+          <t>B- 46.17</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6593,7 +6597,7 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>09-08 15:00</t>
+          <t>09-08 16:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -6607,7 +6611,7 @@
         </is>
       </c>
       <c r="U28" s="4" t="n">
-        <v>3.2429</v>
+        <v>4.77</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
@@ -6617,7 +6621,7 @@
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>1.97%~2.07%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
@@ -6625,31 +6629,35 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z28" s="3"/>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟用于生产性支出,包括偿还债务、补充流动资金、项目建设等</t>
+          <t>本期债券的募集资金拟全部用于偿还到期债券本金。[23中财C3,24中财G2,24中财C1,22中财G2]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,财信证券股份有限公司,华泰联合证券有限责任公司,申万宏源证券有限公司</t>
+          <t>华泰联合证券有限责任公司,国金证券股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr">
@@ -6659,7 +6667,7 @@
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>湖南建设投资集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第四期)</t>
+          <t>中国中金财富证券有限公司2026年面向专业投资者公开发行公司债券(第五期)(品种一)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
@@ -6669,7 +6677,7 @@
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2031-09-10</t>
+          <t>2029-09-10</t>
         </is>
       </c>
       <c r="AK28" s="3"/>
@@ -6680,7 +6688,7 @@
       </c>
       <c r="AM28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AN28" s="3" t="inlineStr">
@@ -6690,32 +6698,32 @@
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
@@ -6748,74 +6756,74 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26重庆银行绿债01</t>
+          <t>26中财10</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>09-08 18:00</t>
+          <t>09-08 19:00</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>222680021.IB</t>
+          <t>246023.SH</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>50.0</v>
+        <v>20.0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>50.0</v>
+        <v>18.0</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>33.94</v>
+        <v>34.28</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>24重庆银行绿色债01(柜台)</t>
+          <t>26中财G8</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>264D</t>
+          <t>4.79Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.4794</t>
+          <t>1.7439</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7300</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>重庆银行股份有限公司</t>
+          <t>中国中金财富证券有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>B+ 57.32</t>
+          <t>B- 46.17</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6825,7 +6833,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>09-08 09:00</t>
+          <t>09-08 16:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -6839,17 +6847,17 @@
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.58</v>
+        <v>4.94</v>
       </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.55%~1.65%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -6864,38 +6872,38 @@
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准,用于《绿色金融支持项目目录(2025年版)》规定的绿色产业项目,优先投向符合《多边可持续金融共同分类目录》的绿色产业项目；重庆银行2026年绿色金融债券(第一期)募集资金拟投放绿色产业项目14个,金额合计人民币50.06亿元；本期债券募集资金应全部用于支持绿色项目的发展,可以直接将绿色金融债券募集资金用于发放绿色项目贷款,闲置资金也可以投资于非金融企业发行的绿色债券以及具有良好信用等级和市场流动性的货币市场工具；确保在债券存续期内,募集资金全部用于绿色项目贷款[重庆银行2026年绿色金融债券(第一期)]</t>
+          <t>本期债券的募集资金拟全部用于偿还到期债券本金。[23中财C3,24中财G2,24中财C1,22中财G2]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,中国邮政储蓄银行股份有限公司,国投证券股份有限公司,国泰海通证券股份有限公司,江苏银行股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,申万宏源证券有限公司,中国银行股份有限公司,国开证券股份有限公司,中国银河证券股份有限公司,西南证券股份有限公司,中银国际证券股份有限公司,东方证券股份有限公司,招商证券股份有限公司</t>
+          <t>华泰联合证券有限责任公司,国金证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG29" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>重庆银行股份有限公司2026年绿色金融债券(第一期)</t>
+          <t>中国中金财富证券有限公司2026年面向专业投资者公开发行公司债券(第五期)(品种二)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6905,18 +6913,18 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2029-09-10</t>
+          <t>2031-09-10</t>
         </is>
       </c>
       <c r="AK29" s="3"/>
       <c r="AL29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t/>
         </is>
       </c>
       <c r="AM29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AN29" s="3" t="inlineStr">
@@ -6936,22 +6944,22 @@
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6984,7 +6992,7 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26中财G9</t>
+          <t>国新发04</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6994,7 +7002,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>246022.SH</t>
+          <t>246053.SH</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -7003,55 +7011,55 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>20.0</v>
+        <v>30.0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>22.0</v>
+        <v>30.0</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.20 ~ 2.10</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>41.94</v>
+        <v>34.94</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26中财G7</t>
+          <t>25国新发展MTN001(科创债)</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2.79Y</t>
+          <t>2.14Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.6629</t>
+          <t>1.6469</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>1.6650/1.6500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>中国中金财富证券有限公司</t>
+          <t>国新发展投资管理有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>B- 46.17</t>
+          <t>C- 24.17</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7075,17 +7083,17 @@
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>4.77</v>
+        <v>3.61</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -7100,23 +7108,23 @@
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金拟全部用于偿还到期债券本金。[23中财C3,24中财G2,24中财C1,22中财G2]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将30亿元全部用于偿还有息负债。</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,国金证券股份有限公司</t>
+          <t>中信证券股份有限公司,国新证券股份有限公司,招商证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
@@ -7131,7 +7139,7 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>中国中金财富证券有限公司2026年面向专业投资者公开发行公司债券(第五期)(品种一)</t>
+          <t>国新发展投资管理有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -7165,11 +7173,7 @@
           <t>金融</t>
         </is>
       </c>
-      <c r="AP30" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
+      <c r="AP30" s="3"/>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
           <t>非银</t>
@@ -7177,17 +7181,17 @@
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -7220,7 +7224,7 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26中财10</t>
+          <t>26东北Y2</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -7230,64 +7234,64 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>246023.SH</t>
+          <t>524939.SZ</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.90 ~ 2.90</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>34.28</v>
+        <v>79.28</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>26中财G8</t>
+          <t>26东北Y1</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>4.79Y</t>
+          <t>4.87Y+N</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.7439</t>
+          <t>2.2467</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>--/1.7300</t>
+          <t>2.2400/2.2000</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>中国中金财富证券有限公司</t>
+          <t>东北证券股份有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>B- 46.17</t>
+          <t>B- 38.24</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7297,7 +7301,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>09-08 16:00</t>
+          <t>09-08 15:00</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
@@ -7311,17 +7315,17 @@
         </is>
       </c>
       <c r="U31" s="4" t="n">
-        <v>4.94</v>
+        <v>3.02</v>
       </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>2.13%~2.23%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
@@ -7336,38 +7340,38 @@
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>吉林省-长春市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金拟全部用于偿还到期债券本金。[23中财C3,24中财G2,24中财C1,22中财G2]</t>
+          <t>本期债券发行总额为不超过10亿元(含10亿元)，募集资金扣除发行费用后，拟全部用于偿还债券期限在1年期以上的公司债券。[23东北01,24东北C1]</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,国金证券股份有限公司</t>
+          <t>长城证券股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>证券公司债</t>
+          <t>证券公司次级债</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>中国中金财富证券有限公司2026年面向专业投资者公开发行公司债券(第五期)(品种二)</t>
+          <t>东北证券股份有限公司2026年面向专业投资者公开发行永续次级债券(第二期)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -7388,7 +7392,7 @@
       </c>
       <c r="AM31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN31" s="3" t="inlineStr">
@@ -7403,7 +7407,7 @@
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
@@ -7438,12 +7442,12 @@
       </c>
       <c r="AW31" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX31" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY31" s="3" t="inlineStr">
@@ -7456,7 +7460,7 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>国新发04</t>
+          <t>26GTHTY6</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7466,12 +7470,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>246053.SH</t>
+          <t>246011.SH</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
@@ -7482,48 +7486,48 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.10</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>34.94</v>
+        <v>47.28</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>25国新发展MTN001(科创债)</t>
+          <t>26GTHTY5</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>2.14Y</t>
+          <t>4.74Y+N</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.6469</t>
+          <t>1.8652</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8750/1.8700</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>国新发展投资管理有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C- 24.17</t>
+          <t>A- 66.49</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7533,7 +7537,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>09-08 16:00</t>
+          <t>09-08 15:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -7547,17 +7551,17 @@
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.61</v>
+        <v>3.95</v>
       </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -7572,28 +7576,28 @@
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将30亿元全部用于偿还有息负债。</t>
+          <t>本期债券募集资金30亿元拟用于补充公司业务运营等日常生产经营所需流动资金。发行人承诺募集资金用于补充流动资金的部分中不超过10%用于融资融券、股票质押、衍生品等资本消耗型业务。</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,国新证券股份有限公司,招商证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>申万宏源证券有限公司,国投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司次级债</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
@@ -7603,7 +7607,7 @@
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>国新发展投资管理有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>国泰海通证券股份有限公司2026年面向专业投资者公开发行永续次级债券(第六期)</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7613,7 +7617,7 @@
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2029-09-10</t>
+          <t>2031-09-10</t>
         </is>
       </c>
       <c r="AK32" s="3"/>
@@ -7624,7 +7628,7 @@
       </c>
       <c r="AM32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AN32" s="3" t="inlineStr">
@@ -7637,7 +7641,11 @@
           <t>金融</t>
         </is>
       </c>
-      <c r="AP32" s="3"/>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
           <t>非银</t>
@@ -7645,17 +7653,17 @@
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7670,12 +7678,12 @@
       </c>
       <c r="AW32" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX32" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY32" s="3" t="inlineStr">
@@ -7688,108 +7696,110 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26东北Y2</t>
+          <t>26华能SCP011</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>09-08 19:00</t>
+          <t>09-08 18:00</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>524939.SZ</t>
+          <t>012682220.IB</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>0.18Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>1.26 ~ 1.46</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>2.2</v>
+        <v>1.33</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>79.28</v>
+        <v>14.9</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>26华能SCP010</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>43D</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>1.4600</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>--/1.4600</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>华能国际电力股份有限公司</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>B- 45.00</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>09-08 09:00</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t>26东北Y1</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t>4.87Y+N</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>2.2467</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t>2.2400/2.2000</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>东北证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t>B- 38.24</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t>09-08 15:00</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U33" s="4" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="V33" s="3"/>
+        <v>1.22</v>
+      </c>
+      <c r="V33" s="4" t="n">
+        <v>1.02</v>
+      </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>2.13%~2.23%</t>
+          <t>1.44%~1.48%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -7797,45 +7807,41 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z33" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>吉林省-长春市</t>
+          <t>河北省-保定市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行总额为不超过10亿元(含10亿元)，募集资金扣除发行费用后，拟全部用于偿还债券期限在1年期以上的公司债券。[23东北01,24东北C1]</t>
+          <t>发行人本期发行超短期融资券发行规模为人民币25亿元,募集资金将用于补充发行人营运资金、调整债务结构、偿还银行借款及即将到期的债券。</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>长城证券股份有限公司</t>
+          <t>渤海银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>证券公司次级债</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>东北证券股份有限公司2026年面向专业投资者公开发行永续次级债券(第二期)</t>
+          <t>华能国际电力股份有限公司2026年度第十一期超短期融资券</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7845,60 +7851,60 @@
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2031-09-10</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="AK33" s="3"/>
       <c r="AL33" s="3" t="inlineStr">
         <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>火电</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AO33" s="3" t="inlineStr">
-        <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AQ33" s="3" t="inlineStr">
-        <is>
-          <t>非银</t>
-        </is>
-      </c>
-      <c r="AR33" s="3" t="inlineStr">
-        <is>
-          <t>证券</t>
-        </is>
-      </c>
-      <c r="AS33" s="3" t="inlineStr">
-        <is>
-          <t>券商</t>
-        </is>
-      </c>
-      <c r="AT33" s="3" t="inlineStr">
-        <is>
-          <t>证券</t>
-        </is>
-      </c>
-      <c r="AU33" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV33" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -7906,12 +7912,12 @@
       </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX33" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY33" s="3" t="inlineStr">
@@ -7924,7 +7930,7 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26GTHTY6</t>
+          <t>26城建K1</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -7934,64 +7940,64 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>246011.SH</t>
+          <t>245937.SH</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>30.0</v>
+        <v>9.0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>30.0</v>
+        <v>13.0</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.10 ~ 2.10</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.88</v>
+        <v>1.58</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>47.28</v>
+        <v>32.94</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>26GTHTY5</t>
+          <t>24京城建MTN004</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>4.74Y+N</t>
+          <t>3.19Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.8652</t>
+          <t>1.7013</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>1.8750/1.8700</t>
+          <t>--/1.7000</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>北京城建集团有限责任公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>A- 66.49</t>
+          <t>C- 22.01</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -8001,7 +8007,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>09-08 15:00</t>
+          <t>09-08 16:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -8015,48 +8021,40 @@
         </is>
       </c>
       <c r="U34" s="4" t="n">
-        <v>3.95</v>
+        <v>3.4308</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X34" s="3" t="inlineStr">
-        <is>
-          <t>1.82%~1.92%</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X34" s="3"/>
       <c r="Y34" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z34" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金30亿元拟用于补充公司业务运营等日常生产经营所需流动资金。发行人承诺募集资金用于补充流动资金的部分中不超过10%用于融资融券、股票质押、衍生品等资本消耗型业务。</t>
+          <t>本期债券发行金额为不超过18亿元(含18亿元)，募集资金拟用于生产性支出,包括偿还公司债务、补充公司流动资金等符合法律法规要求的用途。</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>申万宏源证券有限公司,国投证券股份有限公司</t>
+          <t>中信证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,招商证券股份有限公司,国信证券股份有限公司,首创证券股份有限公司,第一创业证券承销保荐有限责任公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>证券公司次级债</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
@@ -8071,7 +8069,7 @@
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司2026年面向专业投资者公开发行永续次级债券(第六期)</t>
+          <t>北京城建集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -8081,7 +8079,7 @@
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2031-09-10</t>
+          <t>2029-09-10</t>
         </is>
       </c>
       <c r="AK34" s="3"/>
@@ -8102,32 +8100,32 @@
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>房屋建筑</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>其他房建</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -8142,12 +8140,12 @@
       </c>
       <c r="AW34" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX34" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY34" s="3" t="inlineStr">
@@ -8160,74 +8158,74 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26华能SCP011</t>
+          <t>26腾旺产投02</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>09-08 18:00</t>
+          <t>09-08 19:00</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>012682220.IB</t>
+          <t>520447.SZ</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>0.18Y</t>
+          <t>5+2</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>25.0</v>
+        <v>2.0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>25.0</v>
+        <v>2.0</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.26 ~ 1.46</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.33</v>
+        <v>2.0</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>14.9</v>
+        <v>47.44</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>26华能SCP010</t>
+          <t>26腾旺产投01</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>43D</t>
+          <t>4.74Y+2.00Y</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.4600</t>
+          <t>2.0180</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>--/1.4600</t>
+          <t>2.0300/1.9800</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>华能国际电力股份有限公司</t>
+          <t>肇庆腾旺产业投资集团有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>B- 45.00</t>
+          <t>B 52.50</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8237,7 +8235,7 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>09-08 09:00</t>
+          <t>09-08 15:00</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
@@ -8247,93 +8245,103 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="U35" s="4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V35" s="4" t="n">
-        <v>1.02</v>
-      </c>
+        <v>5.1</v>
+      </c>
+      <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>1.44%~1.48%</t>
+          <t>2.05%~2.15%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>河北省-保定市</t>
+          <t>广东省-肇庆市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行超短期融资券发行规模为人民币25亿元,募集资金将用于补充发行人营运资金、调整债务结构、偿还银行借款及即将到期的债券。</t>
+          <t>本期公司债券募集资金扣除发行费用后，拟将不超过2.00亿元用于偿还到期债务</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司,中国民生银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD35" s="3"/>
+          <t>天风证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr">
+        <is>
+          <t>广东粤财融资担保集团有限公司</t>
+        </is>
+      </c>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>华能国际电力股份有限公司2026年度第十一期超短期融资券</t>
+          <t>肇庆腾旺产业投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2026-11-13</t>
-        </is>
-      </c>
-      <c r="AK35" s="3"/>
+          <t>2033-09-10</t>
+        </is>
+      </c>
+      <c r="AK35" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL35" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="AM35" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
           <t>产业</t>
@@ -8341,42 +8349,42 @@
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>房地产</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>房地产服务</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>火电</t>
+          <t>其他房地产服务</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-10</t>
         </is>
       </c>
       <c r="AV35" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW35" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX35" s="3" t="inlineStr">
@@ -8394,74 +8402,74 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26城建K1</t>
+          <t>26大同D2</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>09-08 19:00</t>
+          <t>09-08 17:00</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>245937.SH</t>
+          <t>283781.SH</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.48Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>13.0</v>
+        <v>1.5</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.10 ~ 2.10</t>
+          <t>1.80 ~ 2.09</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1.58</v>
+        <v>2.09</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>32.94</v>
+        <v>85.79</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>24京城建MTN004</t>
+          <t>25大同D1</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>3.19Y</t>
+          <t>52D</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.7013</t>
+          <t>2.6629</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>--/1.7000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>北京城建集团有限责任公司</t>
+          <t>大同证券有限责任公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C- 22.01</t>
+          <t>C- 10.11</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8471,7 +8479,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>09-08 16:00</t>
+          <t>09-08 13:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -8481,49 +8489,53 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U36" s="4" t="n">
-        <v>3.4308</v>
+        <v>1.0</v>
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X36" s="3"/>
+          <t>7+</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>2.49%~2.53%</t>
+        </is>
+      </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>山西省-大同市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行金额为不超过18亿元(含18亿元)，募集资金拟用于生产性支出,包括偿还公司债务、补充公司流动资金等符合法律法规要求的用途。</t>
+          <t>本期债券发行规模不超过人民币2.00亿元(含2.00亿元)。本期债券募集资金扣除发行费用后,1.50亿元用于偿还到期短期公司债券,剩余部分用于补充流动资金。[26大同D1]</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中信建投证券股份有限公司,中国国际金融股份有限公司,招商证券股份有限公司,国信证券股份有限公司,首创证券股份有限公司,第一创业证券承销保荐有限责任公司</t>
+          <t>大同证券有限责任公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司债</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG36" s="3" t="inlineStr">
@@ -8533,23 +8545,23 @@
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>北京城建集团有限责任公司2026年面向专业投资者公开发行科技创新公司债券(第一期)(品种一)</t>
+          <t>大同证券有限责任公司2026年面向专业投资者非公开发行短期公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2029-09-10</t>
+          <t>2027-03-03</t>
         </is>
       </c>
       <c r="AK36" s="3"/>
       <c r="AL36" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AM36" s="3" t="inlineStr">
@@ -8559,37 +8571,37 @@
       </c>
       <c r="AN36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>房屋建筑</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>其他房建</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8622,7 +8634,7 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26腾旺产投02</t>
+          <t>26惠控03</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8632,19 +8644,19 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>520447.SZ</t>
+          <t>283945.SH</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>5+2</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
         <v>2.0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
@@ -8652,44 +8664,44 @@
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>2.0</v>
+        <v>2.22</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>47.44</v>
+        <v>69.44</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>26腾旺产投01</t>
+          <t>24惠控03</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>4.74Y+2.00Y</t>
+          <t>2.49Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>2.0180</t>
+          <t>1.7669</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>2.0300/1.9800</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>肇庆腾旺产业投资集团有限公司</t>
+          <t>无锡市惠山国有投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>B 52.50</t>
+          <t>C+ 33.03</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8709,53 +8721,45 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="U37" s="4" t="n">
-        <v>5.1</v>
+        <v>3.03</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>2.05%~2.15%</t>
+          <t>2.15%~2.25%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z37" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>广东省-肇庆市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后，拟将不超过2.00亿元用于偿还到期债务</t>
+          <t>本期债券募集资金扣除发行费用后,仅用于偿还回售的公司债券本金[23惠控02]</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>天风证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD37" s="3" t="inlineStr">
-        <is>
-          <t>广东粤财融资担保集团有限公司</t>
-        </is>
-      </c>
+          <t>天风证券股份有限公司,国联民生证券承销保荐有限公司</t>
+        </is>
+      </c>
+      <c r="AD37" s="3"/>
       <c r="AE37" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -8768,12 +8772,12 @@
       </c>
       <c r="AG37" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>肇庆腾旺产业投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>无锡市惠山国有投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8783,72 +8787,68 @@
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2033-09-10</t>
-        </is>
-      </c>
-      <c r="AK37" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2033-09-09</t>
+        </is>
+      </c>
+      <c r="AK37" s="3"/>
       <c r="AL37" s="3" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM37" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="AO37" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ37" s="3" t="inlineStr">
-        <is>
-          <t>房地产</t>
-        </is>
-      </c>
-      <c r="AR37" s="3" t="inlineStr">
-        <is>
-          <t>房地产服务</t>
-        </is>
-      </c>
-      <c r="AS37" s="3" t="inlineStr">
-        <is>
-          <t>其他房地产服务</t>
-        </is>
-      </c>
-      <c r="AT37" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU37" s="3" t="inlineStr">
-        <is>
-          <t>2031-09-10</t>
-        </is>
-      </c>
       <c r="AV37" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW37" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX37" s="3" t="inlineStr">
